--- a/AnalisisFinanciero/data/890903939_2024-12-31_Estado_de_cambios_en_el_patrimonio_traduccion.xlsx
+++ b/AnalisisFinanciero/data/890903939_2024-12-31_Estado_de_cambios_en_el_patrimonio_traduccion.xlsx
@@ -1,12 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFA486B-0B59-4B2E-8A54-6D823EA5FD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Hoja1" state="visible" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -184,46 +209,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
       <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
     </font>
     <font>
-      <color theme="1"/>
-      <sz val="9"/>
       <name val="Helvetica Neue"/>
-    </font>
-    <font/>
-    <font>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <b/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Helvetica Neue"/>
+      <name val="Arial"/>
+      <sz val="10.00"/>
+      <family val="2"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
       <b/>
-      <color theme="1"/>
-      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
+    </font>
+    <font>
       <name val="Helvetica Neue"/>
+      <sz val="9.00"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,29 +262,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCCC"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="27">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -269,7 +427,68 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -278,10 +497,49 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -318,12 +576,32 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -344,7 +622,9 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -352,9 +632,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -365,92 +662,198 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf borderId="1" applyBorder="1"/>
+    <xf fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" applyFont="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" applyBorder="1"/>
+    <xf borderId="6" applyBorder="1"/>
+    <xf fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="4" applyFont="1" fillId="7" applyFill="1" borderId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="8" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="9" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf borderId="13" applyBorder="1"/>
+    <xf fontId="3" applyFont="1" fillId="10" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" fillId="12" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" fillId="13" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="14" applyFill="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="15" applyFill="1" borderId="19" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="16" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="17" applyFill="1" borderId="21" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="6" applyFont="1" fillId="18" applyFill="1" borderId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf borderId="23" applyBorder="1"/>
+    <xf fontId="3" applyFont="1" fillId="19" applyFill="1" borderId="24" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" fillId="20" applyFill="1" borderId="25" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" fillId="21" applyFill="1" borderId="26" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
+    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="17" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="12" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="14" quotePrefix="0" pivotButton="0" borderId="13" applyBorder="1"/>
+    <xf xfId="24" quotePrefix="0" pivotButton="0" borderId="23" applyBorder="1"/>
+    <xf xfId="27" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="21" applyFill="1" borderId="26" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="15" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="10" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="6" quotePrefix="0" pivotButton="0" borderId="5" applyBorder="1"/>
+    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="13" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="9" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="10" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="20" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="15" applyFill="1" borderId="19" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="26" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="20" applyFill="1" borderId="25" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="11" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="7" applyFill="1" borderId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="22" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="17" applyFill="1" borderId="21" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="25" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="19" applyFill="1" borderId="24" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="7" quotePrefix="0" pivotButton="0" borderId="6" applyBorder="1"/>
+    <xf xfId="2" quotePrefix="0" pivotButton="0" borderId="1" applyBorder="1"/>
+    <xf xfId="18" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="13" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="12" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="8" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="23" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="18" applyFill="1" borderId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="21" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="16" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="19" quotePrefix="0" pivotButton="0" fontId="6" applyFont="1" fillId="14" applyFill="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf xfId="16" quotePrefix="0" pivotButton="0" fontId="4" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -466,56 +869,116 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -553,15 +1016,15 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
@@ -622,32 +1085,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
+            <a:satMod val="170000"/>
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:satMod val="120000"/>
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -656,22 +1119,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH1000"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.00" customHeight="1" defaultColWidth="14.47"/>
   <cols>
-    <col min="1" max="4" width="3.43" customWidth="1"/>
-    <col min="5" max="5" width="63" customWidth="1"/>
-    <col min="6" max="30" width="18.86" customWidth="1"/>
-    <col min="31" max="31" width="27.14" customWidth="1"/>
-    <col min="32" max="34" width="18.86" customWidth="1"/>
+    <col min="1" max="4" width="3.43" customWidth="1" hidden="0"/>
+    <col min="5" max="5" width="63.04" customWidth="1" hidden="0"/>
+    <col min="6" max="30" width="18.89" customWidth="1" hidden="0"/>
+    <col min="31" max="31" width="27.11" customWidth="1" hidden="0"/>
+    <col min="32" max="34" width="18.89" customWidth="1" hidden="0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" ht="12.75" customHeight="true">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -709,7 +1180,7 @@
       <c r="AG1" s="3"/>
       <c r="AH1" s="4"/>
     </row>
-    <row r="2" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" ht="12.75" customHeight="true">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -763,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="54" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" ht="54.00" customHeight="true">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -843,7 +1314,7 @@
       </c>
       <c r="AH3" s="8"/>
     </row>
-    <row r="4" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" ht="12.75" customHeight="true">
       <c r="A4" s="11" t="s">
         <v>32</v>
       </c>
@@ -881,7 +1352,7 @@
       <c r="AG4" s="12"/>
       <c r="AH4" s="12"/>
     </row>
-    <row r="5" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" ht="12.75" customHeight="true">
       <c r="A5" s="13"/>
       <c r="B5" s="14" t="s">
         <v>33</v>
@@ -919,7 +1390,7 @@
       <c r="AG5" s="15"/>
       <c r="AH5" s="15"/>
     </row>
-    <row r="6" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" ht="12.75" customHeight="true">
       <c r="A6" s="13"/>
       <c r="B6" s="16"/>
       <c r="C6" s="17" t="s">
@@ -981,7 +1452,7 @@
         <v>1505755984</v>
       </c>
     </row>
-    <row r="7" ht="27.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" ht="27.75" customHeight="true">
       <c r="A7" s="13"/>
       <c r="B7" s="16"/>
       <c r="C7" s="20" t="s">
@@ -1019,7 +1490,7 @@
       <c r="AG7" s="15"/>
       <c r="AH7" s="15"/>
     </row>
-    <row r="8" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" ht="12.75" customHeight="true">
       <c r="A8" s="13"/>
       <c r="B8" s="16"/>
       <c r="C8" s="17" t="s">
@@ -1081,7 +1552,7 @@
         <v>1505755984</v>
       </c>
     </row>
-    <row r="9" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" ht="12.75" customHeight="true">
       <c r="A9" s="13"/>
       <c r="B9" s="16"/>
       <c r="C9" s="14" t="s">
@@ -1119,7 +1590,7 @@
       <c r="AG9" s="15"/>
       <c r="AH9" s="15"/>
     </row>
-    <row r="10" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" ht="12.75" customHeight="true">
       <c r="A10" s="13"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -1157,7 +1628,7 @@
       <c r="AG10" s="12"/>
       <c r="AH10" s="12"/>
     </row>
-    <row r="11" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" ht="12.75" customHeight="true">
       <c r="A11" s="13"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -1201,7 +1672,7 @@
         <v>44074579</v>
       </c>
     </row>
-    <row r="12" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" ht="12.75" customHeight="true">
       <c r="A12" s="13"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1247,7 +1718,7 @@
         <v>-180115</v>
       </c>
     </row>
-    <row r="13" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" ht="12.75" customHeight="true">
       <c r="A13" s="13"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -1297,7 +1768,7 @@
         <v>43894464</v>
       </c>
     </row>
-    <row r="14" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" ht="12.75" customHeight="true">
       <c r="A14" s="13"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -1335,7 +1806,7 @@
       <c r="AG14" s="12"/>
       <c r="AH14" s="12"/>
     </row>
-    <row r="15" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" ht="12.75" customHeight="true">
       <c r="A15" s="13"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -1373,7 +1844,7 @@
       <c r="AG15" s="15"/>
       <c r="AH15" s="15"/>
     </row>
-    <row r="16" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" ht="12.75" customHeight="true">
       <c r="A16" s="13"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -1411,7 +1882,7 @@
       <c r="AG16" s="12"/>
       <c r="AH16" s="12"/>
     </row>
-    <row r="17" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" ht="12.75" customHeight="true">
       <c r="A17" s="13"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -1449,7 +1920,7 @@
       <c r="AG17" s="15"/>
       <c r="AH17" s="15"/>
     </row>
-    <row r="18" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" ht="12.75" customHeight="true">
       <c r="A18" s="13"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -1499,7 +1970,7 @@
         <v>120003787</v>
       </c>
     </row>
-    <row r="19" ht="27.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" ht="27.75" customHeight="true">
       <c r="A19" s="13"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -1537,7 +2008,7 @@
       <c r="AG19" s="15"/>
       <c r="AH19" s="15"/>
     </row>
-    <row r="20" ht="27.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" ht="27.75" customHeight="true">
       <c r="A20" s="13"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -1581,7 +2052,7 @@
         <v>-171775</v>
       </c>
     </row>
-    <row r="21" ht="27.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" ht="27.75" customHeight="true">
       <c r="A21" s="13"/>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -1625,7 +2096,7 @@
         <v>-117556832</v>
       </c>
     </row>
-    <row r="22" ht="55.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" ht="55.50" customHeight="true">
       <c r="A22" s="13"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -1663,7 +2134,7 @@
       <c r="AG22" s="12"/>
       <c r="AH22" s="12"/>
     </row>
-    <row r="23" ht="55.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" ht="55.50" customHeight="true">
       <c r="A23" s="13"/>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -1701,7 +2172,7 @@
       <c r="AG23" s="15"/>
       <c r="AH23" s="15"/>
     </row>
-    <row r="24" ht="55.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" ht="55.50" customHeight="true">
       <c r="A24" s="13"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -1739,7 +2210,7 @@
       <c r="AG24" s="12"/>
       <c r="AH24" s="12"/>
     </row>
-    <row r="25" ht="69.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" ht="69.75" customHeight="true">
       <c r="A25" s="13"/>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -1777,7 +2248,7 @@
       <c r="AG25" s="15"/>
       <c r="AH25" s="15"/>
     </row>
-    <row r="26" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" ht="12.75" customHeight="true">
       <c r="A26" s="13"/>
       <c r="B26" s="16"/>
       <c r="C26" s="25"/>
@@ -1833,7 +2304,7 @@
         <v>46169644</v>
       </c>
     </row>
-    <row r="27" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" ht="12.75" customHeight="true">
       <c r="A27" s="23"/>
       <c r="B27" s="25"/>
       <c r="C27" s="20" t="s">
@@ -1895,7 +2366,7 @@
         <v>1551925628</v>
       </c>
     </row>
-    <row r="28" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" ht="12.75" customHeight="true">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1931,7 +2402,7 @@
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
     </row>
-    <row r="29" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" ht="12.75" customHeight="true">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1967,7 +2438,7 @@
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
     </row>
-    <row r="30" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" ht="12.75" customHeight="true">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2003,7 +2474,7 @@
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
     </row>
-    <row r="31" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" ht="12.75" customHeight="true">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2039,7 +2510,7 @@
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
     </row>
-    <row r="32" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" ht="12.75" customHeight="true">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2075,7 +2546,7 @@
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
     </row>
-    <row r="33" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="33" ht="12.75" customHeight="true">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2111,7 +2582,7 @@
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
     </row>
-    <row r="34" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="34" ht="12.75" customHeight="true">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2147,7 +2618,7 @@
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
     </row>
-    <row r="35" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="35" ht="12.75" customHeight="true">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2183,7 +2654,7 @@
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
     </row>
-    <row r="36" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="36" ht="12.75" customHeight="true">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2219,7 +2690,7 @@
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
     </row>
-    <row r="37" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="37" ht="12.75" customHeight="true">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2255,7 +2726,7 @@
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
     </row>
-    <row r="38" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="38" ht="12.75" customHeight="true">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2291,7 +2762,7 @@
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
     </row>
-    <row r="39" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="39" ht="12.75" customHeight="true">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2327,7 +2798,7 @@
       <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
     </row>
-    <row r="40" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="40" ht="12.75" customHeight="true">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2363,7 +2834,7 @@
       <c r="AG40" s="1"/>
       <c r="AH40" s="1"/>
     </row>
-    <row r="41" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="41" ht="12.75" customHeight="true">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2399,7 +2870,7 @@
       <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
     </row>
-    <row r="42" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="42" ht="12.75" customHeight="true">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2435,7 +2906,7 @@
       <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
     </row>
-    <row r="43" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="43" ht="12.75" customHeight="true">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2471,7 +2942,7 @@
       <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
     </row>
-    <row r="44" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="44" ht="12.75" customHeight="true">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2507,7 +2978,7 @@
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
     </row>
-    <row r="45" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="45" ht="12.75" customHeight="true">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2543,7 +3014,7 @@
       <c r="AG45" s="1"/>
       <c r="AH45" s="1"/>
     </row>
-    <row r="46" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="46" ht="12.75" customHeight="true">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2579,7 +3050,7 @@
       <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="47" ht="12.75" customHeight="true">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2615,7 +3086,7 @@
       <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
     </row>
-    <row r="48" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="48" ht="12.75" customHeight="true">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2651,7 +3122,7 @@
       <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>
     </row>
-    <row r="49" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="49" ht="12.75" customHeight="true">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2687,7 +3158,7 @@
       <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
     </row>
-    <row r="50" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="50" ht="12.75" customHeight="true">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2723,7 +3194,7 @@
       <c r="AG50" s="1"/>
       <c r="AH50" s="1"/>
     </row>
-    <row r="51" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="51" ht="12.75" customHeight="true">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2759,7 +3230,7 @@
       <c r="AG51" s="1"/>
       <c r="AH51" s="1"/>
     </row>
-    <row r="52" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="52" ht="12.75" customHeight="true">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2795,7 +3266,7 @@
       <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
     </row>
-    <row r="53" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="53" ht="12.75" customHeight="true">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2831,7 +3302,7 @@
       <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
     </row>
-    <row r="54" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="54" ht="12.75" customHeight="true">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2867,7 +3338,7 @@
       <c r="AG54" s="1"/>
       <c r="AH54" s="1"/>
     </row>
-    <row r="55" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="55" ht="12.75" customHeight="true">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2903,7 +3374,7 @@
       <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
     </row>
-    <row r="56" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="56" ht="12.75" customHeight="true">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2939,7 +3410,7 @@
       <c r="AG56" s="1"/>
       <c r="AH56" s="1"/>
     </row>
-    <row r="57" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="57" ht="12.75" customHeight="true">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2975,7 +3446,7 @@
       <c r="AG57" s="1"/>
       <c r="AH57" s="1"/>
     </row>
-    <row r="58" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="58" ht="12.75" customHeight="true">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3011,7 +3482,7 @@
       <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
     </row>
-    <row r="59" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="59" ht="12.75" customHeight="true">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3047,7 +3518,7 @@
       <c r="AG59" s="1"/>
       <c r="AH59" s="1"/>
     </row>
-    <row r="60" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="60" ht="12.75" customHeight="true">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3083,7 +3554,7 @@
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
     </row>
-    <row r="61" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="61" ht="12.75" customHeight="true">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3119,7 +3590,7 @@
       <c r="AG61" s="1"/>
       <c r="AH61" s="1"/>
     </row>
-    <row r="62" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="62" ht="12.75" customHeight="true">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3155,7 +3626,7 @@
       <c r="AG62" s="1"/>
       <c r="AH62" s="1"/>
     </row>
-    <row r="63" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="63" ht="12.75" customHeight="true">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3191,7 +3662,7 @@
       <c r="AG63" s="1"/>
       <c r="AH63" s="1"/>
     </row>
-    <row r="64" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="64" ht="12.75" customHeight="true">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3227,7 +3698,7 @@
       <c r="AG64" s="1"/>
       <c r="AH64" s="1"/>
     </row>
-    <row r="65" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="65" ht="12.75" customHeight="true">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3263,7 +3734,7 @@
       <c r="AG65" s="1"/>
       <c r="AH65" s="1"/>
     </row>
-    <row r="66" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="66" ht="12.75" customHeight="true">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3299,7 +3770,7 @@
       <c r="AG66" s="1"/>
       <c r="AH66" s="1"/>
     </row>
-    <row r="67" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="67" ht="12.75" customHeight="true">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3335,7 +3806,7 @@
       <c r="AG67" s="1"/>
       <c r="AH67" s="1"/>
     </row>
-    <row r="68" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="68" ht="12.75" customHeight="true">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3371,7 +3842,7 @@
       <c r="AG68" s="1"/>
       <c r="AH68" s="1"/>
     </row>
-    <row r="69" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="69" ht="12.75" customHeight="true">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3407,7 +3878,7 @@
       <c r="AG69" s="1"/>
       <c r="AH69" s="1"/>
     </row>
-    <row r="70" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="70" ht="12.75" customHeight="true">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3443,7 +3914,7 @@
       <c r="AG70" s="1"/>
       <c r="AH70" s="1"/>
     </row>
-    <row r="71" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="71" ht="12.75" customHeight="true">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3479,7 +3950,7 @@
       <c r="AG71" s="1"/>
       <c r="AH71" s="1"/>
     </row>
-    <row r="72" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="72" ht="12.75" customHeight="true">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3515,7 +3986,7 @@
       <c r="AG72" s="1"/>
       <c r="AH72" s="1"/>
     </row>
-    <row r="73" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="73" ht="12.75" customHeight="true">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3551,7 +4022,7 @@
       <c r="AG73" s="1"/>
       <c r="AH73" s="1"/>
     </row>
-    <row r="74" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="74" ht="12.75" customHeight="true">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3587,7 +4058,7 @@
       <c r="AG74" s="1"/>
       <c r="AH74" s="1"/>
     </row>
-    <row r="75" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="75" ht="12.75" customHeight="true">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3623,7 +4094,7 @@
       <c r="AG75" s="1"/>
       <c r="AH75" s="1"/>
     </row>
-    <row r="76" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="76" ht="12.75" customHeight="true">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3659,7 +4130,7 @@
       <c r="AG76" s="1"/>
       <c r="AH76" s="1"/>
     </row>
-    <row r="77" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="77" ht="12.75" customHeight="true">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3695,7 +4166,7 @@
       <c r="AG77" s="1"/>
       <c r="AH77" s="1"/>
     </row>
-    <row r="78" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="78" ht="12.75" customHeight="true">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3731,7 +4202,7 @@
       <c r="AG78" s="1"/>
       <c r="AH78" s="1"/>
     </row>
-    <row r="79" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="79" ht="12.75" customHeight="true">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3767,7 +4238,7 @@
       <c r="AG79" s="1"/>
       <c r="AH79" s="1"/>
     </row>
-    <row r="80" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="80" ht="12.75" customHeight="true">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3803,7 +4274,7 @@
       <c r="AG80" s="1"/>
       <c r="AH80" s="1"/>
     </row>
-    <row r="81" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="81" ht="12.75" customHeight="true">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3839,7 +4310,7 @@
       <c r="AG81" s="1"/>
       <c r="AH81" s="1"/>
     </row>
-    <row r="82" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="82" ht="12.75" customHeight="true">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3875,7 +4346,7 @@
       <c r="AG82" s="1"/>
       <c r="AH82" s="1"/>
     </row>
-    <row r="83" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="83" ht="12.75" customHeight="true">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3911,7 +4382,7 @@
       <c r="AG83" s="1"/>
       <c r="AH83" s="1"/>
     </row>
-    <row r="84" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="84" ht="12.75" customHeight="true">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3947,7 +4418,7 @@
       <c r="AG84" s="1"/>
       <c r="AH84" s="1"/>
     </row>
-    <row r="85" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="85" ht="12.75" customHeight="true">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3983,7 +4454,7 @@
       <c r="AG85" s="1"/>
       <c r="AH85" s="1"/>
     </row>
-    <row r="86" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="86" ht="12.75" customHeight="true">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4019,7 +4490,7 @@
       <c r="AG86" s="1"/>
       <c r="AH86" s="1"/>
     </row>
-    <row r="87" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="87" ht="12.75" customHeight="true">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4055,7 +4526,7 @@
       <c r="AG87" s="1"/>
       <c r="AH87" s="1"/>
     </row>
-    <row r="88" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="88" ht="12.75" customHeight="true">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4091,7 +4562,7 @@
       <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
     </row>
-    <row r="89" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="89" ht="12.75" customHeight="true">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4127,7 +4598,7 @@
       <c r="AG89" s="1"/>
       <c r="AH89" s="1"/>
     </row>
-    <row r="90" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="90" ht="12.75" customHeight="true">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4163,7 +4634,7 @@
       <c r="AG90" s="1"/>
       <c r="AH90" s="1"/>
     </row>
-    <row r="91" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="91" ht="12.75" customHeight="true">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4199,7 +4670,7 @@
       <c r="AG91" s="1"/>
       <c r="AH91" s="1"/>
     </row>
-    <row r="92" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="92" ht="12.75" customHeight="true">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4235,7 +4706,7 @@
       <c r="AG92" s="1"/>
       <c r="AH92" s="1"/>
     </row>
-    <row r="93" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="93" ht="12.75" customHeight="true">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4271,7 +4742,7 @@
       <c r="AG93" s="1"/>
       <c r="AH93" s="1"/>
     </row>
-    <row r="94" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="94" ht="12.75" customHeight="true">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4307,7 +4778,7 @@
       <c r="AG94" s="1"/>
       <c r="AH94" s="1"/>
     </row>
-    <row r="95" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="95" ht="12.75" customHeight="true">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4343,7 +4814,7 @@
       <c r="AG95" s="1"/>
       <c r="AH95" s="1"/>
     </row>
-    <row r="96" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="96" ht="12.75" customHeight="true">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4379,7 +4850,7 @@
       <c r="AG96" s="1"/>
       <c r="AH96" s="1"/>
     </row>
-    <row r="97" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="97" ht="12.75" customHeight="true">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4415,7 +4886,7 @@
       <c r="AG97" s="1"/>
       <c r="AH97" s="1"/>
     </row>
-    <row r="98" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="98" ht="12.75" customHeight="true">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4451,7 +4922,7 @@
       <c r="AG98" s="1"/>
       <c r="AH98" s="1"/>
     </row>
-    <row r="99" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="99" ht="12.75" customHeight="true">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4487,7 +4958,7 @@
       <c r="AG99" s="1"/>
       <c r="AH99" s="1"/>
     </row>
-    <row r="100" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="100" ht="12.75" customHeight="true">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4523,7 +4994,7 @@
       <c r="AG100" s="1"/>
       <c r="AH100" s="1"/>
     </row>
-    <row r="101" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="101" ht="12.75" customHeight="true">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4559,7 +5030,7 @@
       <c r="AG101" s="1"/>
       <c r="AH101" s="1"/>
     </row>
-    <row r="102" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="102" ht="12.75" customHeight="true">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4595,7 +5066,7 @@
       <c r="AG102" s="1"/>
       <c r="AH102" s="1"/>
     </row>
-    <row r="103" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="103" ht="12.75" customHeight="true">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4631,7 +5102,7 @@
       <c r="AG103" s="1"/>
       <c r="AH103" s="1"/>
     </row>
-    <row r="104" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="104" ht="12.75" customHeight="true">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4667,7 +5138,7 @@
       <c r="AG104" s="1"/>
       <c r="AH104" s="1"/>
     </row>
-    <row r="105" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="105" ht="12.75" customHeight="true">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4703,7 +5174,7 @@
       <c r="AG105" s="1"/>
       <c r="AH105" s="1"/>
     </row>
-    <row r="106" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="106" ht="12.75" customHeight="true">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -4739,7 +5210,7 @@
       <c r="AG106" s="1"/>
       <c r="AH106" s="1"/>
     </row>
-    <row r="107" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="107" ht="12.75" customHeight="true">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4775,7 +5246,7 @@
       <c r="AG107" s="1"/>
       <c r="AH107" s="1"/>
     </row>
-    <row r="108" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="108" ht="12.75" customHeight="true">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4811,7 +5282,7 @@
       <c r="AG108" s="1"/>
       <c r="AH108" s="1"/>
     </row>
-    <row r="109" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="109" ht="12.75" customHeight="true">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4847,7 +5318,7 @@
       <c r="AG109" s="1"/>
       <c r="AH109" s="1"/>
     </row>
-    <row r="110" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="110" ht="12.75" customHeight="true">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4883,7 +5354,7 @@
       <c r="AG110" s="1"/>
       <c r="AH110" s="1"/>
     </row>
-    <row r="111" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="111" ht="12.75" customHeight="true">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4919,7 +5390,7 @@
       <c r="AG111" s="1"/>
       <c r="AH111" s="1"/>
     </row>
-    <row r="112" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="112" ht="12.75" customHeight="true">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4955,7 +5426,7 @@
       <c r="AG112" s="1"/>
       <c r="AH112" s="1"/>
     </row>
-    <row r="113" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="113" ht="12.75" customHeight="true">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4991,7 +5462,7 @@
       <c r="AG113" s="1"/>
       <c r="AH113" s="1"/>
     </row>
-    <row r="114" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="114" ht="12.75" customHeight="true">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5027,7 +5498,7 @@
       <c r="AG114" s="1"/>
       <c r="AH114" s="1"/>
     </row>
-    <row r="115" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="115" ht="12.75" customHeight="true">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5063,7 +5534,7 @@
       <c r="AG115" s="1"/>
       <c r="AH115" s="1"/>
     </row>
-    <row r="116" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="116" ht="12.75" customHeight="true">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5099,7 +5570,7 @@
       <c r="AG116" s="1"/>
       <c r="AH116" s="1"/>
     </row>
-    <row r="117" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="117" ht="12.75" customHeight="true">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5135,7 +5606,7 @@
       <c r="AG117" s="1"/>
       <c r="AH117" s="1"/>
     </row>
-    <row r="118" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="118" ht="12.75" customHeight="true">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5171,7 +5642,7 @@
       <c r="AG118" s="1"/>
       <c r="AH118" s="1"/>
     </row>
-    <row r="119" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="119" ht="12.75" customHeight="true">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -5207,7 +5678,7 @@
       <c r="AG119" s="1"/>
       <c r="AH119" s="1"/>
     </row>
-    <row r="120" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="120" ht="12.75" customHeight="true">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -5243,7 +5714,7 @@
       <c r="AG120" s="1"/>
       <c r="AH120" s="1"/>
     </row>
-    <row r="121" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="121" ht="12.75" customHeight="true">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -5279,7 +5750,7 @@
       <c r="AG121" s="1"/>
       <c r="AH121" s="1"/>
     </row>
-    <row r="122" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="122" ht="12.75" customHeight="true">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -5315,7 +5786,7 @@
       <c r="AG122" s="1"/>
       <c r="AH122" s="1"/>
     </row>
-    <row r="123" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="123" ht="12.75" customHeight="true">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -5351,7 +5822,7 @@
       <c r="AG123" s="1"/>
       <c r="AH123" s="1"/>
     </row>
-    <row r="124" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="124" ht="12.75" customHeight="true">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5387,7 +5858,7 @@
       <c r="AG124" s="1"/>
       <c r="AH124" s="1"/>
     </row>
-    <row r="125" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="125" ht="12.75" customHeight="true">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5423,7 +5894,7 @@
       <c r="AG125" s="1"/>
       <c r="AH125" s="1"/>
     </row>
-    <row r="126" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="126" ht="12.75" customHeight="true">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5459,7 +5930,7 @@
       <c r="AG126" s="1"/>
       <c r="AH126" s="1"/>
     </row>
-    <row r="127" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="127" ht="12.75" customHeight="true">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5495,7 +5966,7 @@
       <c r="AG127" s="1"/>
       <c r="AH127" s="1"/>
     </row>
-    <row r="128" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="128" ht="12.75" customHeight="true">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5531,7 +6002,7 @@
       <c r="AG128" s="1"/>
       <c r="AH128" s="1"/>
     </row>
-    <row r="129" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="129" ht="12.75" customHeight="true">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5567,7 +6038,7 @@
       <c r="AG129" s="1"/>
       <c r="AH129" s="1"/>
     </row>
-    <row r="130" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="130" ht="12.75" customHeight="true">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5603,7 +6074,7 @@
       <c r="AG130" s="1"/>
       <c r="AH130" s="1"/>
     </row>
-    <row r="131" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="131" ht="12.75" customHeight="true">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5639,7 +6110,7 @@
       <c r="AG131" s="1"/>
       <c r="AH131" s="1"/>
     </row>
-    <row r="132" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="132" ht="12.75" customHeight="true">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5675,7 +6146,7 @@
       <c r="AG132" s="1"/>
       <c r="AH132" s="1"/>
     </row>
-    <row r="133" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="133" ht="12.75" customHeight="true">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5711,7 +6182,7 @@
       <c r="AG133" s="1"/>
       <c r="AH133" s="1"/>
     </row>
-    <row r="134" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="134" ht="12.75" customHeight="true">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5747,7 +6218,7 @@
       <c r="AG134" s="1"/>
       <c r="AH134" s="1"/>
     </row>
-    <row r="135" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="135" ht="12.75" customHeight="true">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5783,7 +6254,7 @@
       <c r="AG135" s="1"/>
       <c r="AH135" s="1"/>
     </row>
-    <row r="136" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="136" ht="12.75" customHeight="true">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5819,7 +6290,7 @@
       <c r="AG136" s="1"/>
       <c r="AH136" s="1"/>
     </row>
-    <row r="137" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="137" ht="12.75" customHeight="true">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5855,7 +6326,7 @@
       <c r="AG137" s="1"/>
       <c r="AH137" s="1"/>
     </row>
-    <row r="138" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="138" ht="12.75" customHeight="true">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5891,7 +6362,7 @@
       <c r="AG138" s="1"/>
       <c r="AH138" s="1"/>
     </row>
-    <row r="139" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="139" ht="12.75" customHeight="true">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5927,7 +6398,7 @@
       <c r="AG139" s="1"/>
       <c r="AH139" s="1"/>
     </row>
-    <row r="140" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="140" ht="12.75" customHeight="true">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5963,7 +6434,7 @@
       <c r="AG140" s="1"/>
       <c r="AH140" s="1"/>
     </row>
-    <row r="141" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="141" ht="12.75" customHeight="true">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5999,7 +6470,7 @@
       <c r="AG141" s="1"/>
       <c r="AH141" s="1"/>
     </row>
-    <row r="142" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="142" ht="12.75" customHeight="true">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -6035,7 +6506,7 @@
       <c r="AG142" s="1"/>
       <c r="AH142" s="1"/>
     </row>
-    <row r="143" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="143" ht="12.75" customHeight="true">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -6071,7 +6542,7 @@
       <c r="AG143" s="1"/>
       <c r="AH143" s="1"/>
     </row>
-    <row r="144" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="144" ht="12.75" customHeight="true">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -6107,7 +6578,7 @@
       <c r="AG144" s="1"/>
       <c r="AH144" s="1"/>
     </row>
-    <row r="145" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="145" ht="12.75" customHeight="true">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -6143,7 +6614,7 @@
       <c r="AG145" s="1"/>
       <c r="AH145" s="1"/>
     </row>
-    <row r="146" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="146" ht="12.75" customHeight="true">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -6179,7 +6650,7 @@
       <c r="AG146" s="1"/>
       <c r="AH146" s="1"/>
     </row>
-    <row r="147" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="147" ht="12.75" customHeight="true">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -6215,7 +6686,7 @@
       <c r="AG147" s="1"/>
       <c r="AH147" s="1"/>
     </row>
-    <row r="148" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="148" ht="12.75" customHeight="true">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -6251,7 +6722,7 @@
       <c r="AG148" s="1"/>
       <c r="AH148" s="1"/>
     </row>
-    <row r="149" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="149" ht="12.75" customHeight="true">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -6287,7 +6758,7 @@
       <c r="AG149" s="1"/>
       <c r="AH149" s="1"/>
     </row>
-    <row r="150" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="150" ht="12.75" customHeight="true">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -6323,7 +6794,7 @@
       <c r="AG150" s="1"/>
       <c r="AH150" s="1"/>
     </row>
-    <row r="151" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="151" ht="12.75" customHeight="true">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -6359,7 +6830,7 @@
       <c r="AG151" s="1"/>
       <c r="AH151" s="1"/>
     </row>
-    <row r="152" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="152" ht="12.75" customHeight="true">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -6395,7 +6866,7 @@
       <c r="AG152" s="1"/>
       <c r="AH152" s="1"/>
     </row>
-    <row r="153" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="153" ht="12.75" customHeight="true">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -6431,7 +6902,7 @@
       <c r="AG153" s="1"/>
       <c r="AH153" s="1"/>
     </row>
-    <row r="154" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="154" ht="12.75" customHeight="true">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -6467,7 +6938,7 @@
       <c r="AG154" s="1"/>
       <c r="AH154" s="1"/>
     </row>
-    <row r="155" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="155" ht="12.75" customHeight="true">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -6503,7 +6974,7 @@
       <c r="AG155" s="1"/>
       <c r="AH155" s="1"/>
     </row>
-    <row r="156" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="156" ht="12.75" customHeight="true">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6539,7 +7010,7 @@
       <c r="AG156" s="1"/>
       <c r="AH156" s="1"/>
     </row>
-    <row r="157" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="157" ht="12.75" customHeight="true">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6575,7 +7046,7 @@
       <c r="AG157" s="1"/>
       <c r="AH157" s="1"/>
     </row>
-    <row r="158" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="158" ht="12.75" customHeight="true">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6611,7 +7082,7 @@
       <c r="AG158" s="1"/>
       <c r="AH158" s="1"/>
     </row>
-    <row r="159" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="159" ht="12.75" customHeight="true">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6647,7 +7118,7 @@
       <c r="AG159" s="1"/>
       <c r="AH159" s="1"/>
     </row>
-    <row r="160" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="160" ht="12.75" customHeight="true">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6683,7 +7154,7 @@
       <c r="AG160" s="1"/>
       <c r="AH160" s="1"/>
     </row>
-    <row r="161" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="161" ht="12.75" customHeight="true">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6719,7 +7190,7 @@
       <c r="AG161" s="1"/>
       <c r="AH161" s="1"/>
     </row>
-    <row r="162" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="162" ht="12.75" customHeight="true">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6755,7 +7226,7 @@
       <c r="AG162" s="1"/>
       <c r="AH162" s="1"/>
     </row>
-    <row r="163" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="163" ht="12.75" customHeight="true">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6791,7 +7262,7 @@
       <c r="AG163" s="1"/>
       <c r="AH163" s="1"/>
     </row>
-    <row r="164" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="164" ht="12.75" customHeight="true">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6827,7 +7298,7 @@
       <c r="AG164" s="1"/>
       <c r="AH164" s="1"/>
     </row>
-    <row r="165" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="165" ht="12.75" customHeight="true">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6863,7 +7334,7 @@
       <c r="AG165" s="1"/>
       <c r="AH165" s="1"/>
     </row>
-    <row r="166" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="166" ht="12.75" customHeight="true">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6899,7 +7370,7 @@
       <c r="AG166" s="1"/>
       <c r="AH166" s="1"/>
     </row>
-    <row r="167" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="167" ht="12.75" customHeight="true">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6935,7 +7406,7 @@
       <c r="AG167" s="1"/>
       <c r="AH167" s="1"/>
     </row>
-    <row r="168" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="168" ht="12.75" customHeight="true">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6971,7 +7442,7 @@
       <c r="AG168" s="1"/>
       <c r="AH168" s="1"/>
     </row>
-    <row r="169" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="169" ht="12.75" customHeight="true">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -7007,7 +7478,7 @@
       <c r="AG169" s="1"/>
       <c r="AH169" s="1"/>
     </row>
-    <row r="170" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="170" ht="12.75" customHeight="true">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -7043,7 +7514,7 @@
       <c r="AG170" s="1"/>
       <c r="AH170" s="1"/>
     </row>
-    <row r="171" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="171" ht="12.75" customHeight="true">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -7079,7 +7550,7 @@
       <c r="AG171" s="1"/>
       <c r="AH171" s="1"/>
     </row>
-    <row r="172" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="172" ht="12.75" customHeight="true">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -7115,7 +7586,7 @@
       <c r="AG172" s="1"/>
       <c r="AH172" s="1"/>
     </row>
-    <row r="173" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="173" ht="12.75" customHeight="true">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -7151,7 +7622,7 @@
       <c r="AG173" s="1"/>
       <c r="AH173" s="1"/>
     </row>
-    <row r="174" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="174" ht="12.75" customHeight="true">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -7187,7 +7658,7 @@
       <c r="AG174" s="1"/>
       <c r="AH174" s="1"/>
     </row>
-    <row r="175" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="175" ht="12.75" customHeight="true">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -7223,7 +7694,7 @@
       <c r="AG175" s="1"/>
       <c r="AH175" s="1"/>
     </row>
-    <row r="176" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="176" ht="12.75" customHeight="true">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -7259,7 +7730,7 @@
       <c r="AG176" s="1"/>
       <c r="AH176" s="1"/>
     </row>
-    <row r="177" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="177" ht="12.75" customHeight="true">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -7295,7 +7766,7 @@
       <c r="AG177" s="1"/>
       <c r="AH177" s="1"/>
     </row>
-    <row r="178" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="178" ht="12.75" customHeight="true">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -7331,7 +7802,7 @@
       <c r="AG178" s="1"/>
       <c r="AH178" s="1"/>
     </row>
-    <row r="179" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="179" ht="12.75" customHeight="true">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -7367,7 +7838,7 @@
       <c r="AG179" s="1"/>
       <c r="AH179" s="1"/>
     </row>
-    <row r="180" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="180" ht="12.75" customHeight="true">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -7403,7 +7874,7 @@
       <c r="AG180" s="1"/>
       <c r="AH180" s="1"/>
     </row>
-    <row r="181" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="181" ht="12.75" customHeight="true">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -7439,7 +7910,7 @@
       <c r="AG181" s="1"/>
       <c r="AH181" s="1"/>
     </row>
-    <row r="182" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="182" ht="12.75" customHeight="true">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -7475,7 +7946,7 @@
       <c r="AG182" s="1"/>
       <c r="AH182" s="1"/>
     </row>
-    <row r="183" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="183" ht="12.75" customHeight="true">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -7511,7 +7982,7 @@
       <c r="AG183" s="1"/>
       <c r="AH183" s="1"/>
     </row>
-    <row r="184" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="184" ht="12.75" customHeight="true">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -7547,7 +8018,7 @@
       <c r="AG184" s="1"/>
       <c r="AH184" s="1"/>
     </row>
-    <row r="185" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="185" ht="12.75" customHeight="true">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -7583,7 +8054,7 @@
       <c r="AG185" s="1"/>
       <c r="AH185" s="1"/>
     </row>
-    <row r="186" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="186" ht="12.75" customHeight="true">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -7619,7 +8090,7 @@
       <c r="AG186" s="1"/>
       <c r="AH186" s="1"/>
     </row>
-    <row r="187" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="187" ht="12.75" customHeight="true">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -7655,7 +8126,7 @@
       <c r="AG187" s="1"/>
       <c r="AH187" s="1"/>
     </row>
-    <row r="188" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="188" ht="12.75" customHeight="true">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -7691,7 +8162,7 @@
       <c r="AG188" s="1"/>
       <c r="AH188" s="1"/>
     </row>
-    <row r="189" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="189" ht="12.75" customHeight="true">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7727,7 +8198,7 @@
       <c r="AG189" s="1"/>
       <c r="AH189" s="1"/>
     </row>
-    <row r="190" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="190" ht="12.75" customHeight="true">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7763,7 +8234,7 @@
       <c r="AG190" s="1"/>
       <c r="AH190" s="1"/>
     </row>
-    <row r="191" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="191" ht="12.75" customHeight="true">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7799,7 +8270,7 @@
       <c r="AG191" s="1"/>
       <c r="AH191" s="1"/>
     </row>
-    <row r="192" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="192" ht="12.75" customHeight="true">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7835,7 +8306,7 @@
       <c r="AG192" s="1"/>
       <c r="AH192" s="1"/>
     </row>
-    <row r="193" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="193" ht="12.75" customHeight="true">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7871,7 +8342,7 @@
       <c r="AG193" s="1"/>
       <c r="AH193" s="1"/>
     </row>
-    <row r="194" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="194" ht="12.75" customHeight="true">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7907,7 +8378,7 @@
       <c r="AG194" s="1"/>
       <c r="AH194" s="1"/>
     </row>
-    <row r="195" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="195" ht="12.75" customHeight="true">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7943,7 +8414,7 @@
       <c r="AG195" s="1"/>
       <c r="AH195" s="1"/>
     </row>
-    <row r="196" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="196" ht="12.75" customHeight="true">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7979,7 +8450,7 @@
       <c r="AG196" s="1"/>
       <c r="AH196" s="1"/>
     </row>
-    <row r="197" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="197" ht="12.75" customHeight="true">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -8015,7 +8486,7 @@
       <c r="AG197" s="1"/>
       <c r="AH197" s="1"/>
     </row>
-    <row r="198" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="198" ht="12.75" customHeight="true">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -8051,7 +8522,7 @@
       <c r="AG198" s="1"/>
       <c r="AH198" s="1"/>
     </row>
-    <row r="199" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="199" ht="12.75" customHeight="true">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -8087,7 +8558,7 @@
       <c r="AG199" s="1"/>
       <c r="AH199" s="1"/>
     </row>
-    <row r="200" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="200" ht="12.75" customHeight="true">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -8123,7 +8594,7 @@
       <c r="AG200" s="1"/>
       <c r="AH200" s="1"/>
     </row>
-    <row r="201" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="201" ht="12.75" customHeight="true">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -8159,7 +8630,7 @@
       <c r="AG201" s="1"/>
       <c r="AH201" s="1"/>
     </row>
-    <row r="202" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="202" ht="12.75" customHeight="true">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -8195,7 +8666,7 @@
       <c r="AG202" s="1"/>
       <c r="AH202" s="1"/>
     </row>
-    <row r="203" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="203" ht="12.75" customHeight="true">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -8231,7 +8702,7 @@
       <c r="AG203" s="1"/>
       <c r="AH203" s="1"/>
     </row>
-    <row r="204" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="204" ht="12.75" customHeight="true">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -8267,7 +8738,7 @@
       <c r="AG204" s="1"/>
       <c r="AH204" s="1"/>
     </row>
-    <row r="205" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="205" ht="12.75" customHeight="true">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -8303,7 +8774,7 @@
       <c r="AG205" s="1"/>
       <c r="AH205" s="1"/>
     </row>
-    <row r="206" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="206" ht="12.75" customHeight="true">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -8339,7 +8810,7 @@
       <c r="AG206" s="1"/>
       <c r="AH206" s="1"/>
     </row>
-    <row r="207" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="207" ht="12.75" customHeight="true">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -8375,7 +8846,7 @@
       <c r="AG207" s="1"/>
       <c r="AH207" s="1"/>
     </row>
-    <row r="208" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="208" ht="12.75" customHeight="true">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -8411,7 +8882,7 @@
       <c r="AG208" s="1"/>
       <c r="AH208" s="1"/>
     </row>
-    <row r="209" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="209" ht="12.75" customHeight="true">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -8447,7 +8918,7 @@
       <c r="AG209" s="1"/>
       <c r="AH209" s="1"/>
     </row>
-    <row r="210" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="210" ht="12.75" customHeight="true">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -8483,7 +8954,7 @@
       <c r="AG210" s="1"/>
       <c r="AH210" s="1"/>
     </row>
-    <row r="211" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="211" ht="12.75" customHeight="true">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -8519,7 +8990,7 @@
       <c r="AG211" s="1"/>
       <c r="AH211" s="1"/>
     </row>
-    <row r="212" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="212" ht="12.75" customHeight="true">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -8555,7 +9026,7 @@
       <c r="AG212" s="1"/>
       <c r="AH212" s="1"/>
     </row>
-    <row r="213" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="213" ht="12.75" customHeight="true">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -8591,7 +9062,7 @@
       <c r="AG213" s="1"/>
       <c r="AH213" s="1"/>
     </row>
-    <row r="214" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="214" ht="12.75" customHeight="true">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -8627,7 +9098,7 @@
       <c r="AG214" s="1"/>
       <c r="AH214" s="1"/>
     </row>
-    <row r="215" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="215" ht="12.75" customHeight="true">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -8663,7 +9134,7 @@
       <c r="AG215" s="1"/>
       <c r="AH215" s="1"/>
     </row>
-    <row r="216" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="216" ht="12.75" customHeight="true">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -8699,7 +9170,7 @@
       <c r="AG216" s="1"/>
       <c r="AH216" s="1"/>
     </row>
-    <row r="217" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="217" ht="12.75" customHeight="true">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -8735,7 +9206,7 @@
       <c r="AG217" s="1"/>
       <c r="AH217" s="1"/>
     </row>
-    <row r="218" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="218" ht="12.75" customHeight="true">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -8771,7 +9242,7 @@
       <c r="AG218" s="1"/>
       <c r="AH218" s="1"/>
     </row>
-    <row r="219" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="219" ht="12.75" customHeight="true">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -8807,7 +9278,7 @@
       <c r="AG219" s="1"/>
       <c r="AH219" s="1"/>
     </row>
-    <row r="220" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="220" ht="12.75" customHeight="true">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8843,7 +9314,7 @@
       <c r="AG220" s="1"/>
       <c r="AH220" s="1"/>
     </row>
-    <row r="221" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="221" ht="12.75" customHeight="true">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8879,7 +9350,7 @@
       <c r="AG221" s="1"/>
       <c r="AH221" s="1"/>
     </row>
-    <row r="222" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="222" ht="12.75" customHeight="true">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8915,7 +9386,7 @@
       <c r="AG222" s="1"/>
       <c r="AH222" s="1"/>
     </row>
-    <row r="223" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="223" ht="12.75" customHeight="true">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8951,7 +9422,7 @@
       <c r="AG223" s="1"/>
       <c r="AH223" s="1"/>
     </row>
-    <row r="224" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="224" ht="12.75" customHeight="true">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8987,7 +9458,7 @@
       <c r="AG224" s="1"/>
       <c r="AH224" s="1"/>
     </row>
-    <row r="225" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="225" ht="12.75" customHeight="true">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -9023,7 +9494,7 @@
       <c r="AG225" s="1"/>
       <c r="AH225" s="1"/>
     </row>
-    <row r="226" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="226" ht="12.75" customHeight="true">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -9059,7 +9530,7 @@
       <c r="AG226" s="1"/>
       <c r="AH226" s="1"/>
     </row>
-    <row r="227" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="227" ht="12.75" customHeight="true">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -9095,7 +9566,7 @@
       <c r="AG227" s="1"/>
       <c r="AH227" s="1"/>
     </row>
-    <row r="228" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="228" ht="12.75" customHeight="true">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -9131,7 +9602,7 @@
       <c r="AG228" s="1"/>
       <c r="AH228" s="1"/>
     </row>
-    <row r="229" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="229" ht="12.75" customHeight="true">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -9167,7 +9638,7 @@
       <c r="AG229" s="1"/>
       <c r="AH229" s="1"/>
     </row>
-    <row r="230" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="230" ht="12.75" customHeight="true">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -9203,7 +9674,7 @@
       <c r="AG230" s="1"/>
       <c r="AH230" s="1"/>
     </row>
-    <row r="231" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="231" ht="12.75" customHeight="true">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -9239,7 +9710,7 @@
       <c r="AG231" s="1"/>
       <c r="AH231" s="1"/>
     </row>
-    <row r="232" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="232" ht="12.75" customHeight="true">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -9275,7 +9746,7 @@
       <c r="AG232" s="1"/>
       <c r="AH232" s="1"/>
     </row>
-    <row r="233" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="233" ht="12.75" customHeight="true">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -9311,7 +9782,7 @@
       <c r="AG233" s="1"/>
       <c r="AH233" s="1"/>
     </row>
-    <row r="234" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="234" ht="12.75" customHeight="true">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -9347,7 +9818,7 @@
       <c r="AG234" s="1"/>
       <c r="AH234" s="1"/>
     </row>
-    <row r="235" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="235" ht="12.75" customHeight="true">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -9383,7 +9854,7 @@
       <c r="AG235" s="1"/>
       <c r="AH235" s="1"/>
     </row>
-    <row r="236" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="236" ht="12.75" customHeight="true">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -9419,7 +9890,7 @@
       <c r="AG236" s="1"/>
       <c r="AH236" s="1"/>
     </row>
-    <row r="237" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="237" ht="12.75" customHeight="true">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -9455,7 +9926,7 @@
       <c r="AG237" s="1"/>
       <c r="AH237" s="1"/>
     </row>
-    <row r="238" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="238" ht="12.75" customHeight="true">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -9491,7 +9962,7 @@
       <c r="AG238" s="1"/>
       <c r="AH238" s="1"/>
     </row>
-    <row r="239" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="239" ht="12.75" customHeight="true">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -9527,7 +9998,7 @@
       <c r="AG239" s="1"/>
       <c r="AH239" s="1"/>
     </row>
-    <row r="240" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="240" ht="12.75" customHeight="true">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -9563,7 +10034,7 @@
       <c r="AG240" s="1"/>
       <c r="AH240" s="1"/>
     </row>
-    <row r="241" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="241" ht="12.75" customHeight="true">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -9599,7 +10070,7 @@
       <c r="AG241" s="1"/>
       <c r="AH241" s="1"/>
     </row>
-    <row r="242" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="242" ht="12.75" customHeight="true">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -9635,7 +10106,7 @@
       <c r="AG242" s="1"/>
       <c r="AH242" s="1"/>
     </row>
-    <row r="243" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="243" ht="12.75" customHeight="true">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -9671,7 +10142,7 @@
       <c r="AG243" s="1"/>
       <c r="AH243" s="1"/>
     </row>
-    <row r="244" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="244" ht="12.75" customHeight="true">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -9707,7 +10178,7 @@
       <c r="AG244" s="1"/>
       <c r="AH244" s="1"/>
     </row>
-    <row r="245" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="245" ht="12.75" customHeight="true">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -9743,7 +10214,7 @@
       <c r="AG245" s="1"/>
       <c r="AH245" s="1"/>
     </row>
-    <row r="246" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="246" ht="12.75" customHeight="true">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -9779,7 +10250,7 @@
       <c r="AG246" s="1"/>
       <c r="AH246" s="1"/>
     </row>
-    <row r="247" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="247" ht="12.75" customHeight="true">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -9815,7 +10286,7 @@
       <c r="AG247" s="1"/>
       <c r="AH247" s="1"/>
     </row>
-    <row r="248" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="248" ht="12.75" customHeight="true">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -9851,7 +10322,7 @@
       <c r="AG248" s="1"/>
       <c r="AH248" s="1"/>
     </row>
-    <row r="249" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="249" ht="12.75" customHeight="true">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -9887,7 +10358,7 @@
       <c r="AG249" s="1"/>
       <c r="AH249" s="1"/>
     </row>
-    <row r="250" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="250" ht="12.75" customHeight="true">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -9923,7 +10394,7 @@
       <c r="AG250" s="1"/>
       <c r="AH250" s="1"/>
     </row>
-    <row r="251" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="251" ht="12.75" customHeight="true">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -9959,7 +10430,7 @@
       <c r="AG251" s="1"/>
       <c r="AH251" s="1"/>
     </row>
-    <row r="252" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="252" ht="12.75" customHeight="true">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -9995,7 +10466,7 @@
       <c r="AG252" s="1"/>
       <c r="AH252" s="1"/>
     </row>
-    <row r="253" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="253" ht="12.75" customHeight="true">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -10031,7 +10502,7 @@
       <c r="AG253" s="1"/>
       <c r="AH253" s="1"/>
     </row>
-    <row r="254" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="254" ht="12.75" customHeight="true">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -10067,7 +10538,7 @@
       <c r="AG254" s="1"/>
       <c r="AH254" s="1"/>
     </row>
-    <row r="255" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="255" ht="12.75" customHeight="true">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -10103,7 +10574,7 @@
       <c r="AG255" s="1"/>
       <c r="AH255" s="1"/>
     </row>
-    <row r="256" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="256" ht="12.75" customHeight="true">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -10139,7 +10610,7 @@
       <c r="AG256" s="1"/>
       <c r="AH256" s="1"/>
     </row>
-    <row r="257" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="257" ht="12.75" customHeight="true">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -10175,7 +10646,7 @@
       <c r="AG257" s="1"/>
       <c r="AH257" s="1"/>
     </row>
-    <row r="258" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="258" ht="12.75" customHeight="true">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -10211,7 +10682,7 @@
       <c r="AG258" s="1"/>
       <c r="AH258" s="1"/>
     </row>
-    <row r="259" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="259" ht="12.75" customHeight="true">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -10247,7 +10718,7 @@
       <c r="AG259" s="1"/>
       <c r="AH259" s="1"/>
     </row>
-    <row r="260" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="260" ht="12.75" customHeight="true">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -10283,7 +10754,7 @@
       <c r="AG260" s="1"/>
       <c r="AH260" s="1"/>
     </row>
-    <row r="261" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="261" ht="12.75" customHeight="true">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -10319,7 +10790,7 @@
       <c r="AG261" s="1"/>
       <c r="AH261" s="1"/>
     </row>
-    <row r="262" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="262" ht="12.75" customHeight="true">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -10355,7 +10826,7 @@
       <c r="AG262" s="1"/>
       <c r="AH262" s="1"/>
     </row>
-    <row r="263" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="263" ht="12.75" customHeight="true">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -10391,7 +10862,7 @@
       <c r="AG263" s="1"/>
       <c r="AH263" s="1"/>
     </row>
-    <row r="264" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="264" ht="12.75" customHeight="true">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -10427,7 +10898,7 @@
       <c r="AG264" s="1"/>
       <c r="AH264" s="1"/>
     </row>
-    <row r="265" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="265" ht="12.75" customHeight="true">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -10463,7 +10934,7 @@
       <c r="AG265" s="1"/>
       <c r="AH265" s="1"/>
     </row>
-    <row r="266" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="266" ht="12.75" customHeight="true">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -10499,7 +10970,7 @@
       <c r="AG266" s="1"/>
       <c r="AH266" s="1"/>
     </row>
-    <row r="267" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="267" ht="12.75" customHeight="true">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -10535,7 +11006,7 @@
       <c r="AG267" s="1"/>
       <c r="AH267" s="1"/>
     </row>
-    <row r="268" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="268" ht="12.75" customHeight="true">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -10571,7 +11042,7 @@
       <c r="AG268" s="1"/>
       <c r="AH268" s="1"/>
     </row>
-    <row r="269" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="269" ht="12.75" customHeight="true">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -10607,7 +11078,7 @@
       <c r="AG269" s="1"/>
       <c r="AH269" s="1"/>
     </row>
-    <row r="270" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="270" ht="12.75" customHeight="true">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -10643,7 +11114,7 @@
       <c r="AG270" s="1"/>
       <c r="AH270" s="1"/>
     </row>
-    <row r="271" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="271" ht="12.75" customHeight="true">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -10679,7 +11150,7 @@
       <c r="AG271" s="1"/>
       <c r="AH271" s="1"/>
     </row>
-    <row r="272" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="272" ht="12.75" customHeight="true">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -10715,7 +11186,7 @@
       <c r="AG272" s="1"/>
       <c r="AH272" s="1"/>
     </row>
-    <row r="273" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="273" ht="12.75" customHeight="true">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -10751,7 +11222,7 @@
       <c r="AG273" s="1"/>
       <c r="AH273" s="1"/>
     </row>
-    <row r="274" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="274" ht="12.75" customHeight="true">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -10787,7 +11258,7 @@
       <c r="AG274" s="1"/>
       <c r="AH274" s="1"/>
     </row>
-    <row r="275" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="275" ht="12.75" customHeight="true">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -10823,7 +11294,7 @@
       <c r="AG275" s="1"/>
       <c r="AH275" s="1"/>
     </row>
-    <row r="276" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="276" ht="12.75" customHeight="true">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -10859,7 +11330,7 @@
       <c r="AG276" s="1"/>
       <c r="AH276" s="1"/>
     </row>
-    <row r="277" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="277" ht="12.75" customHeight="true">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -10895,7 +11366,7 @@
       <c r="AG277" s="1"/>
       <c r="AH277" s="1"/>
     </row>
-    <row r="278" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="278" ht="12.75" customHeight="true">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -10931,7 +11402,7 @@
       <c r="AG278" s="1"/>
       <c r="AH278" s="1"/>
     </row>
-    <row r="279" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="279" ht="12.75" customHeight="true">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -10967,7 +11438,7 @@
       <c r="AG279" s="1"/>
       <c r="AH279" s="1"/>
     </row>
-    <row r="280" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="280" ht="12.75" customHeight="true">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -11003,7 +11474,7 @@
       <c r="AG280" s="1"/>
       <c r="AH280" s="1"/>
     </row>
-    <row r="281" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="281" ht="12.75" customHeight="true">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -11039,7 +11510,7 @@
       <c r="AG281" s="1"/>
       <c r="AH281" s="1"/>
     </row>
-    <row r="282" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="282" ht="12.75" customHeight="true">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -11075,7 +11546,7 @@
       <c r="AG282" s="1"/>
       <c r="AH282" s="1"/>
     </row>
-    <row r="283" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="283" ht="12.75" customHeight="true">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -11111,7 +11582,7 @@
       <c r="AG283" s="1"/>
       <c r="AH283" s="1"/>
     </row>
-    <row r="284" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="284" ht="12.75" customHeight="true">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -11147,7 +11618,7 @@
       <c r="AG284" s="1"/>
       <c r="AH284" s="1"/>
     </row>
-    <row r="285" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="285" ht="12.75" customHeight="true">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -11183,7 +11654,7 @@
       <c r="AG285" s="1"/>
       <c r="AH285" s="1"/>
     </row>
-    <row r="286" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="286" ht="12.75" customHeight="true">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -11219,7 +11690,7 @@
       <c r="AG286" s="1"/>
       <c r="AH286" s="1"/>
     </row>
-    <row r="287" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="287" ht="12.75" customHeight="true">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -11255,7 +11726,7 @@
       <c r="AG287" s="1"/>
       <c r="AH287" s="1"/>
     </row>
-    <row r="288" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="288" ht="12.75" customHeight="true">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -11291,7 +11762,7 @@
       <c r="AG288" s="1"/>
       <c r="AH288" s="1"/>
     </row>
-    <row r="289" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="289" ht="12.75" customHeight="true">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -11327,7 +11798,7 @@
       <c r="AG289" s="1"/>
       <c r="AH289" s="1"/>
     </row>
-    <row r="290" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="290" ht="12.75" customHeight="true">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -11363,7 +11834,7 @@
       <c r="AG290" s="1"/>
       <c r="AH290" s="1"/>
     </row>
-    <row r="291" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="291" ht="12.75" customHeight="true">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -11399,7 +11870,7 @@
       <c r="AG291" s="1"/>
       <c r="AH291" s="1"/>
     </row>
-    <row r="292" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="292" ht="12.75" customHeight="true">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -11435,7 +11906,7 @@
       <c r="AG292" s="1"/>
       <c r="AH292" s="1"/>
     </row>
-    <row r="293" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="293" ht="12.75" customHeight="true">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -11471,7 +11942,7 @@
       <c r="AG293" s="1"/>
       <c r="AH293" s="1"/>
     </row>
-    <row r="294" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="294" ht="12.75" customHeight="true">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -11507,7 +11978,7 @@
       <c r="AG294" s="1"/>
       <c r="AH294" s="1"/>
     </row>
-    <row r="295" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="295" ht="12.75" customHeight="true">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -11543,7 +12014,7 @@
       <c r="AG295" s="1"/>
       <c r="AH295" s="1"/>
     </row>
-    <row r="296" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="296" ht="12.75" customHeight="true">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -11579,7 +12050,7 @@
       <c r="AG296" s="1"/>
       <c r="AH296" s="1"/>
     </row>
-    <row r="297" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="297" ht="12.75" customHeight="true">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -11615,7 +12086,7 @@
       <c r="AG297" s="1"/>
       <c r="AH297" s="1"/>
     </row>
-    <row r="298" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="298" ht="12.75" customHeight="true">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -11651,7 +12122,7 @@
       <c r="AG298" s="1"/>
       <c r="AH298" s="1"/>
     </row>
-    <row r="299" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="299" ht="12.75" customHeight="true">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -11687,7 +12158,7 @@
       <c r="AG299" s="1"/>
       <c r="AH299" s="1"/>
     </row>
-    <row r="300" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="300" ht="12.75" customHeight="true">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -11723,7 +12194,7 @@
       <c r="AG300" s="1"/>
       <c r="AH300" s="1"/>
     </row>
-    <row r="301" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="301" ht="12.75" customHeight="true">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -11759,7 +12230,7 @@
       <c r="AG301" s="1"/>
       <c r="AH301" s="1"/>
     </row>
-    <row r="302" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="302" ht="12.75" customHeight="true">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -11795,7 +12266,7 @@
       <c r="AG302" s="1"/>
       <c r="AH302" s="1"/>
     </row>
-    <row r="303" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="303" ht="12.75" customHeight="true">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -11831,7 +12302,7 @@
       <c r="AG303" s="1"/>
       <c r="AH303" s="1"/>
     </row>
-    <row r="304" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="304" ht="12.75" customHeight="true">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -11867,7 +12338,7 @@
       <c r="AG304" s="1"/>
       <c r="AH304" s="1"/>
     </row>
-    <row r="305" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="305" ht="12.75" customHeight="true">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -11903,7 +12374,7 @@
       <c r="AG305" s="1"/>
       <c r="AH305" s="1"/>
     </row>
-    <row r="306" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="306" ht="12.75" customHeight="true">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -11939,7 +12410,7 @@
       <c r="AG306" s="1"/>
       <c r="AH306" s="1"/>
     </row>
-    <row r="307" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="307" ht="12.75" customHeight="true">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -11975,7 +12446,7 @@
       <c r="AG307" s="1"/>
       <c r="AH307" s="1"/>
     </row>
-    <row r="308" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="308" ht="12.75" customHeight="true">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -12011,7 +12482,7 @@
       <c r="AG308" s="1"/>
       <c r="AH308" s="1"/>
     </row>
-    <row r="309" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="309" ht="12.75" customHeight="true">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -12047,7 +12518,7 @@
       <c r="AG309" s="1"/>
       <c r="AH309" s="1"/>
     </row>
-    <row r="310" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="310" ht="12.75" customHeight="true">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -12083,7 +12554,7 @@
       <c r="AG310" s="1"/>
       <c r="AH310" s="1"/>
     </row>
-    <row r="311" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="311" ht="12.75" customHeight="true">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -12119,7 +12590,7 @@
       <c r="AG311" s="1"/>
       <c r="AH311" s="1"/>
     </row>
-    <row r="312" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="312" ht="12.75" customHeight="true">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -12155,7 +12626,7 @@
       <c r="AG312" s="1"/>
       <c r="AH312" s="1"/>
     </row>
-    <row r="313" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="313" ht="12.75" customHeight="true">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -12191,7 +12662,7 @@
       <c r="AG313" s="1"/>
       <c r="AH313" s="1"/>
     </row>
-    <row r="314" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="314" ht="12.75" customHeight="true">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -12227,7 +12698,7 @@
       <c r="AG314" s="1"/>
       <c r="AH314" s="1"/>
     </row>
-    <row r="315" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="315" ht="12.75" customHeight="true">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -12263,7 +12734,7 @@
       <c r="AG315" s="1"/>
       <c r="AH315" s="1"/>
     </row>
-    <row r="316" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="316" ht="12.75" customHeight="true">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -12299,7 +12770,7 @@
       <c r="AG316" s="1"/>
       <c r="AH316" s="1"/>
     </row>
-    <row r="317" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="317" ht="12.75" customHeight="true">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -12335,7 +12806,7 @@
       <c r="AG317" s="1"/>
       <c r="AH317" s="1"/>
     </row>
-    <row r="318" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="318" ht="12.75" customHeight="true">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -12371,7 +12842,7 @@
       <c r="AG318" s="1"/>
       <c r="AH318" s="1"/>
     </row>
-    <row r="319" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="319" ht="12.75" customHeight="true">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -12407,7 +12878,7 @@
       <c r="AG319" s="1"/>
       <c r="AH319" s="1"/>
     </row>
-    <row r="320" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="320" ht="12.75" customHeight="true">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -12443,7 +12914,7 @@
       <c r="AG320" s="1"/>
       <c r="AH320" s="1"/>
     </row>
-    <row r="321" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="321" ht="12.75" customHeight="true">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -12479,7 +12950,7 @@
       <c r="AG321" s="1"/>
       <c r="AH321" s="1"/>
     </row>
-    <row r="322" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="322" ht="12.75" customHeight="true">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -12515,7 +12986,7 @@
       <c r="AG322" s="1"/>
       <c r="AH322" s="1"/>
     </row>
-    <row r="323" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="323" ht="12.75" customHeight="true">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -12551,7 +13022,7 @@
       <c r="AG323" s="1"/>
       <c r="AH323" s="1"/>
     </row>
-    <row r="324" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="324" ht="12.75" customHeight="true">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -12587,7 +13058,7 @@
       <c r="AG324" s="1"/>
       <c r="AH324" s="1"/>
     </row>
-    <row r="325" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="325" ht="12.75" customHeight="true">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -12623,7 +13094,7 @@
       <c r="AG325" s="1"/>
       <c r="AH325" s="1"/>
     </row>
-    <row r="326" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="326" ht="12.75" customHeight="true">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -12659,7 +13130,7 @@
       <c r="AG326" s="1"/>
       <c r="AH326" s="1"/>
     </row>
-    <row r="327" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="327" ht="12.75" customHeight="true">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -12695,7 +13166,7 @@
       <c r="AG327" s="1"/>
       <c r="AH327" s="1"/>
     </row>
-    <row r="328" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="328" ht="12.75" customHeight="true">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -12731,7 +13202,7 @@
       <c r="AG328" s="1"/>
       <c r="AH328" s="1"/>
     </row>
-    <row r="329" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="329" ht="12.75" customHeight="true">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -12767,7 +13238,7 @@
       <c r="AG329" s="1"/>
       <c r="AH329" s="1"/>
     </row>
-    <row r="330" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="330" ht="12.75" customHeight="true">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -12803,7 +13274,7 @@
       <c r="AG330" s="1"/>
       <c r="AH330" s="1"/>
     </row>
-    <row r="331" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="331" ht="12.75" customHeight="true">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -12839,7 +13310,7 @@
       <c r="AG331" s="1"/>
       <c r="AH331" s="1"/>
     </row>
-    <row r="332" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="332" ht="12.75" customHeight="true">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -12875,7 +13346,7 @@
       <c r="AG332" s="1"/>
       <c r="AH332" s="1"/>
     </row>
-    <row r="333" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="333" ht="12.75" customHeight="true">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -12911,7 +13382,7 @@
       <c r="AG333" s="1"/>
       <c r="AH333" s="1"/>
     </row>
-    <row r="334" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="334" ht="12.75" customHeight="true">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -12947,7 +13418,7 @@
       <c r="AG334" s="1"/>
       <c r="AH334" s="1"/>
     </row>
-    <row r="335" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="335" ht="12.75" customHeight="true">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -12983,7 +13454,7 @@
       <c r="AG335" s="1"/>
       <c r="AH335" s="1"/>
     </row>
-    <row r="336" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="336" ht="12.75" customHeight="true">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -13019,7 +13490,7 @@
       <c r="AG336" s="1"/>
       <c r="AH336" s="1"/>
     </row>
-    <row r="337" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="337" ht="12.75" customHeight="true">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -13055,7 +13526,7 @@
       <c r="AG337" s="1"/>
       <c r="AH337" s="1"/>
     </row>
-    <row r="338" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="338" ht="12.75" customHeight="true">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -13091,7 +13562,7 @@
       <c r="AG338" s="1"/>
       <c r="AH338" s="1"/>
     </row>
-    <row r="339" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="339" ht="12.75" customHeight="true">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -13127,7 +13598,7 @@
       <c r="AG339" s="1"/>
       <c r="AH339" s="1"/>
     </row>
-    <row r="340" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="340" ht="12.75" customHeight="true">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -13163,7 +13634,7 @@
       <c r="AG340" s="1"/>
       <c r="AH340" s="1"/>
     </row>
-    <row r="341" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="341" ht="12.75" customHeight="true">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -13199,7 +13670,7 @@
       <c r="AG341" s="1"/>
       <c r="AH341" s="1"/>
     </row>
-    <row r="342" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="342" ht="12.75" customHeight="true">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -13235,7 +13706,7 @@
       <c r="AG342" s="1"/>
       <c r="AH342" s="1"/>
     </row>
-    <row r="343" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="343" ht="12.75" customHeight="true">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -13271,7 +13742,7 @@
       <c r="AG343" s="1"/>
       <c r="AH343" s="1"/>
     </row>
-    <row r="344" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="344" ht="12.75" customHeight="true">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -13307,7 +13778,7 @@
       <c r="AG344" s="1"/>
       <c r="AH344" s="1"/>
     </row>
-    <row r="345" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="345" ht="12.75" customHeight="true">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -13343,7 +13814,7 @@
       <c r="AG345" s="1"/>
       <c r="AH345" s="1"/>
     </row>
-    <row r="346" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="346" ht="12.75" customHeight="true">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -13379,7 +13850,7 @@
       <c r="AG346" s="1"/>
       <c r="AH346" s="1"/>
     </row>
-    <row r="347" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="347" ht="12.75" customHeight="true">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -13415,7 +13886,7 @@
       <c r="AG347" s="1"/>
       <c r="AH347" s="1"/>
     </row>
-    <row r="348" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="348" ht="12.75" customHeight="true">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -13451,7 +13922,7 @@
       <c r="AG348" s="1"/>
       <c r="AH348" s="1"/>
     </row>
-    <row r="349" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="349" ht="12.75" customHeight="true">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -13487,7 +13958,7 @@
       <c r="AG349" s="1"/>
       <c r="AH349" s="1"/>
     </row>
-    <row r="350" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="350" ht="12.75" customHeight="true">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -13523,7 +13994,7 @@
       <c r="AG350" s="1"/>
       <c r="AH350" s="1"/>
     </row>
-    <row r="351" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="351" ht="12.75" customHeight="true">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -13559,7 +14030,7 @@
       <c r="AG351" s="1"/>
       <c r="AH351" s="1"/>
     </row>
-    <row r="352" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="352" ht="12.75" customHeight="true">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -13595,7 +14066,7 @@
       <c r="AG352" s="1"/>
       <c r="AH352" s="1"/>
     </row>
-    <row r="353" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="353" ht="12.75" customHeight="true">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -13631,7 +14102,7 @@
       <c r="AG353" s="1"/>
       <c r="AH353" s="1"/>
     </row>
-    <row r="354" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="354" ht="12.75" customHeight="true">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -13667,7 +14138,7 @@
       <c r="AG354" s="1"/>
       <c r="AH354" s="1"/>
     </row>
-    <row r="355" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="355" ht="12.75" customHeight="true">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -13703,7 +14174,7 @@
       <c r="AG355" s="1"/>
       <c r="AH355" s="1"/>
     </row>
-    <row r="356" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="356" ht="12.75" customHeight="true">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -13739,7 +14210,7 @@
       <c r="AG356" s="1"/>
       <c r="AH356" s="1"/>
     </row>
-    <row r="357" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="357" ht="12.75" customHeight="true">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -13775,7 +14246,7 @@
       <c r="AG357" s="1"/>
       <c r="AH357" s="1"/>
     </row>
-    <row r="358" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="358" ht="12.75" customHeight="true">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -13811,7 +14282,7 @@
       <c r="AG358" s="1"/>
       <c r="AH358" s="1"/>
     </row>
-    <row r="359" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="359" ht="12.75" customHeight="true">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -13847,7 +14318,7 @@
       <c r="AG359" s="1"/>
       <c r="AH359" s="1"/>
     </row>
-    <row r="360" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="360" ht="12.75" customHeight="true">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -13883,7 +14354,7 @@
       <c r="AG360" s="1"/>
       <c r="AH360" s="1"/>
     </row>
-    <row r="361" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="361" ht="12.75" customHeight="true">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -13919,7 +14390,7 @@
       <c r="AG361" s="1"/>
       <c r="AH361" s="1"/>
     </row>
-    <row r="362" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="362" ht="12.75" customHeight="true">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -13955,7 +14426,7 @@
       <c r="AG362" s="1"/>
       <c r="AH362" s="1"/>
     </row>
-    <row r="363" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="363" ht="12.75" customHeight="true">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -13991,7 +14462,7 @@
       <c r="AG363" s="1"/>
       <c r="AH363" s="1"/>
     </row>
-    <row r="364" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="364" ht="12.75" customHeight="true">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -14027,7 +14498,7 @@
       <c r="AG364" s="1"/>
       <c r="AH364" s="1"/>
     </row>
-    <row r="365" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="365" ht="12.75" customHeight="true">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -14063,7 +14534,7 @@
       <c r="AG365" s="1"/>
       <c r="AH365" s="1"/>
     </row>
-    <row r="366" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="366" ht="12.75" customHeight="true">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -14099,7 +14570,7 @@
       <c r="AG366" s="1"/>
       <c r="AH366" s="1"/>
     </row>
-    <row r="367" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="367" ht="12.75" customHeight="true">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -14135,7 +14606,7 @@
       <c r="AG367" s="1"/>
       <c r="AH367" s="1"/>
     </row>
-    <row r="368" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="368" ht="12.75" customHeight="true">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -14171,7 +14642,7 @@
       <c r="AG368" s="1"/>
       <c r="AH368" s="1"/>
     </row>
-    <row r="369" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="369" ht="12.75" customHeight="true">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -14207,7 +14678,7 @@
       <c r="AG369" s="1"/>
       <c r="AH369" s="1"/>
     </row>
-    <row r="370" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="370" ht="12.75" customHeight="true">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -14243,7 +14714,7 @@
       <c r="AG370" s="1"/>
       <c r="AH370" s="1"/>
     </row>
-    <row r="371" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="371" ht="12.75" customHeight="true">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -14279,7 +14750,7 @@
       <c r="AG371" s="1"/>
       <c r="AH371" s="1"/>
     </row>
-    <row r="372" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="372" ht="12.75" customHeight="true">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -14315,7 +14786,7 @@
       <c r="AG372" s="1"/>
       <c r="AH372" s="1"/>
     </row>
-    <row r="373" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="373" ht="12.75" customHeight="true">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -14351,7 +14822,7 @@
       <c r="AG373" s="1"/>
       <c r="AH373" s="1"/>
     </row>
-    <row r="374" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="374" ht="12.75" customHeight="true">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -14387,7 +14858,7 @@
       <c r="AG374" s="1"/>
       <c r="AH374" s="1"/>
     </row>
-    <row r="375" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="375" ht="12.75" customHeight="true">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -14423,7 +14894,7 @@
       <c r="AG375" s="1"/>
       <c r="AH375" s="1"/>
     </row>
-    <row r="376" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="376" ht="12.75" customHeight="true">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -14459,7 +14930,7 @@
       <c r="AG376" s="1"/>
       <c r="AH376" s="1"/>
     </row>
-    <row r="377" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="377" ht="12.75" customHeight="true">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -14495,7 +14966,7 @@
       <c r="AG377" s="1"/>
       <c r="AH377" s="1"/>
     </row>
-    <row r="378" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="378" ht="12.75" customHeight="true">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -14531,7 +15002,7 @@
       <c r="AG378" s="1"/>
       <c r="AH378" s="1"/>
     </row>
-    <row r="379" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="379" ht="12.75" customHeight="true">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -14567,7 +15038,7 @@
       <c r="AG379" s="1"/>
       <c r="AH379" s="1"/>
     </row>
-    <row r="380" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="380" ht="12.75" customHeight="true">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -14603,7 +15074,7 @@
       <c r="AG380" s="1"/>
       <c r="AH380" s="1"/>
     </row>
-    <row r="381" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="381" ht="12.75" customHeight="true">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -14639,7 +15110,7 @@
       <c r="AG381" s="1"/>
       <c r="AH381" s="1"/>
     </row>
-    <row r="382" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="382" ht="12.75" customHeight="true">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -14675,7 +15146,7 @@
       <c r="AG382" s="1"/>
       <c r="AH382" s="1"/>
     </row>
-    <row r="383" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="383" ht="12.75" customHeight="true">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -14711,7 +15182,7 @@
       <c r="AG383" s="1"/>
       <c r="AH383" s="1"/>
     </row>
-    <row r="384" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="384" ht="12.75" customHeight="true">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -14747,7 +15218,7 @@
       <c r="AG384" s="1"/>
       <c r="AH384" s="1"/>
     </row>
-    <row r="385" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="385" ht="12.75" customHeight="true">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -14783,7 +15254,7 @@
       <c r="AG385" s="1"/>
       <c r="AH385" s="1"/>
     </row>
-    <row r="386" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="386" ht="12.75" customHeight="true">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -14819,7 +15290,7 @@
       <c r="AG386" s="1"/>
       <c r="AH386" s="1"/>
     </row>
-    <row r="387" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="387" ht="12.75" customHeight="true">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -14855,7 +15326,7 @@
       <c r="AG387" s="1"/>
       <c r="AH387" s="1"/>
     </row>
-    <row r="388" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="388" ht="12.75" customHeight="true">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -14891,7 +15362,7 @@
       <c r="AG388" s="1"/>
       <c r="AH388" s="1"/>
     </row>
-    <row r="389" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="389" ht="12.75" customHeight="true">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -14927,7 +15398,7 @@
       <c r="AG389" s="1"/>
       <c r="AH389" s="1"/>
     </row>
-    <row r="390" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="390" ht="12.75" customHeight="true">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -14963,7 +15434,7 @@
       <c r="AG390" s="1"/>
       <c r="AH390" s="1"/>
     </row>
-    <row r="391" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="391" ht="12.75" customHeight="true">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -14999,7 +15470,7 @@
       <c r="AG391" s="1"/>
       <c r="AH391" s="1"/>
     </row>
-    <row r="392" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="392" ht="12.75" customHeight="true">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -15035,7 +15506,7 @@
       <c r="AG392" s="1"/>
       <c r="AH392" s="1"/>
     </row>
-    <row r="393" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="393" ht="12.75" customHeight="true">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -15071,7 +15542,7 @@
       <c r="AG393" s="1"/>
       <c r="AH393" s="1"/>
     </row>
-    <row r="394" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="394" ht="12.75" customHeight="true">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -15107,7 +15578,7 @@
       <c r="AG394" s="1"/>
       <c r="AH394" s="1"/>
     </row>
-    <row r="395" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="395" ht="12.75" customHeight="true">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -15143,7 +15614,7 @@
       <c r="AG395" s="1"/>
       <c r="AH395" s="1"/>
     </row>
-    <row r="396" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="396" ht="12.75" customHeight="true">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -15179,7 +15650,7 @@
       <c r="AG396" s="1"/>
       <c r="AH396" s="1"/>
     </row>
-    <row r="397" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="397" ht="12.75" customHeight="true">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -15215,7 +15686,7 @@
       <c r="AG397" s="1"/>
       <c r="AH397" s="1"/>
     </row>
-    <row r="398" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="398" ht="12.75" customHeight="true">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -15251,7 +15722,7 @@
       <c r="AG398" s="1"/>
       <c r="AH398" s="1"/>
     </row>
-    <row r="399" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="399" ht="12.75" customHeight="true">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -15287,7 +15758,7 @@
       <c r="AG399" s="1"/>
       <c r="AH399" s="1"/>
     </row>
-    <row r="400" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="400" ht="12.75" customHeight="true">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -15323,7 +15794,7 @@
       <c r="AG400" s="1"/>
       <c r="AH400" s="1"/>
     </row>
-    <row r="401" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="401" ht="12.75" customHeight="true">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -15359,7 +15830,7 @@
       <c r="AG401" s="1"/>
       <c r="AH401" s="1"/>
     </row>
-    <row r="402" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="402" ht="12.75" customHeight="true">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -15395,7 +15866,7 @@
       <c r="AG402" s="1"/>
       <c r="AH402" s="1"/>
     </row>
-    <row r="403" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="403" ht="12.75" customHeight="true">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -15431,7 +15902,7 @@
       <c r="AG403" s="1"/>
       <c r="AH403" s="1"/>
     </row>
-    <row r="404" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="404" ht="12.75" customHeight="true">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -15467,7 +15938,7 @@
       <c r="AG404" s="1"/>
       <c r="AH404" s="1"/>
     </row>
-    <row r="405" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="405" ht="12.75" customHeight="true">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -15503,7 +15974,7 @@
       <c r="AG405" s="1"/>
       <c r="AH405" s="1"/>
     </row>
-    <row r="406" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="406" ht="12.75" customHeight="true">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -15539,7 +16010,7 @@
       <c r="AG406" s="1"/>
       <c r="AH406" s="1"/>
     </row>
-    <row r="407" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="407" ht="12.75" customHeight="true">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -15575,7 +16046,7 @@
       <c r="AG407" s="1"/>
       <c r="AH407" s="1"/>
     </row>
-    <row r="408" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="408" ht="12.75" customHeight="true">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -15611,7 +16082,7 @@
       <c r="AG408" s="1"/>
       <c r="AH408" s="1"/>
     </row>
-    <row r="409" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="409" ht="12.75" customHeight="true">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -15647,7 +16118,7 @@
       <c r="AG409" s="1"/>
       <c r="AH409" s="1"/>
     </row>
-    <row r="410" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="410" ht="12.75" customHeight="true">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -15683,7 +16154,7 @@
       <c r="AG410" s="1"/>
       <c r="AH410" s="1"/>
     </row>
-    <row r="411" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="411" ht="12.75" customHeight="true">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -15719,7 +16190,7 @@
       <c r="AG411" s="1"/>
       <c r="AH411" s="1"/>
     </row>
-    <row r="412" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="412" ht="12.75" customHeight="true">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -15755,7 +16226,7 @@
       <c r="AG412" s="1"/>
       <c r="AH412" s="1"/>
     </row>
-    <row r="413" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="413" ht="12.75" customHeight="true">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -15791,7 +16262,7 @@
       <c r="AG413" s="1"/>
       <c r="AH413" s="1"/>
     </row>
-    <row r="414" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="414" ht="12.75" customHeight="true">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -15827,7 +16298,7 @@
       <c r="AG414" s="1"/>
       <c r="AH414" s="1"/>
     </row>
-    <row r="415" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="415" ht="12.75" customHeight="true">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -15863,7 +16334,7 @@
       <c r="AG415" s="1"/>
       <c r="AH415" s="1"/>
     </row>
-    <row r="416" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="416" ht="12.75" customHeight="true">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -15899,7 +16370,7 @@
       <c r="AG416" s="1"/>
       <c r="AH416" s="1"/>
     </row>
-    <row r="417" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="417" ht="12.75" customHeight="true">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -15935,7 +16406,7 @@
       <c r="AG417" s="1"/>
       <c r="AH417" s="1"/>
     </row>
-    <row r="418" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="418" ht="12.75" customHeight="true">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -15971,7 +16442,7 @@
       <c r="AG418" s="1"/>
       <c r="AH418" s="1"/>
     </row>
-    <row r="419" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="419" ht="12.75" customHeight="true">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -16007,7 +16478,7 @@
       <c r="AG419" s="1"/>
       <c r="AH419" s="1"/>
     </row>
-    <row r="420" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="420" ht="12.75" customHeight="true">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -16043,7 +16514,7 @@
       <c r="AG420" s="1"/>
       <c r="AH420" s="1"/>
     </row>
-    <row r="421" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="421" ht="12.75" customHeight="true">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -16079,7 +16550,7 @@
       <c r="AG421" s="1"/>
       <c r="AH421" s="1"/>
     </row>
-    <row r="422" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="422" ht="12.75" customHeight="true">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -16115,7 +16586,7 @@
       <c r="AG422" s="1"/>
       <c r="AH422" s="1"/>
     </row>
-    <row r="423" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="423" ht="12.75" customHeight="true">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -16151,7 +16622,7 @@
       <c r="AG423" s="1"/>
       <c r="AH423" s="1"/>
     </row>
-    <row r="424" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="424" ht="12.75" customHeight="true">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -16187,7 +16658,7 @@
       <c r="AG424" s="1"/>
       <c r="AH424" s="1"/>
     </row>
-    <row r="425" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="425" ht="12.75" customHeight="true">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -16223,7 +16694,7 @@
       <c r="AG425" s="1"/>
       <c r="AH425" s="1"/>
     </row>
-    <row r="426" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="426" ht="12.75" customHeight="true">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -16259,7 +16730,7 @@
       <c r="AG426" s="1"/>
       <c r="AH426" s="1"/>
     </row>
-    <row r="427" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="427" ht="12.75" customHeight="true">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -16295,7 +16766,7 @@
       <c r="AG427" s="1"/>
       <c r="AH427" s="1"/>
     </row>
-    <row r="428" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="428" ht="12.75" customHeight="true">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -16331,7 +16802,7 @@
       <c r="AG428" s="1"/>
       <c r="AH428" s="1"/>
     </row>
-    <row r="429" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="429" ht="12.75" customHeight="true">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -16367,7 +16838,7 @@
       <c r="AG429" s="1"/>
       <c r="AH429" s="1"/>
     </row>
-    <row r="430" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="430" ht="12.75" customHeight="true">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -16403,7 +16874,7 @@
       <c r="AG430" s="1"/>
       <c r="AH430" s="1"/>
     </row>
-    <row r="431" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="431" ht="12.75" customHeight="true">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -16439,7 +16910,7 @@
       <c r="AG431" s="1"/>
       <c r="AH431" s="1"/>
     </row>
-    <row r="432" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="432" ht="12.75" customHeight="true">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -16475,7 +16946,7 @@
       <c r="AG432" s="1"/>
       <c r="AH432" s="1"/>
     </row>
-    <row r="433" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="433" ht="12.75" customHeight="true">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -16511,7 +16982,7 @@
       <c r="AG433" s="1"/>
       <c r="AH433" s="1"/>
     </row>
-    <row r="434" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="434" ht="12.75" customHeight="true">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -16547,7 +17018,7 @@
       <c r="AG434" s="1"/>
       <c r="AH434" s="1"/>
     </row>
-    <row r="435" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="435" ht="12.75" customHeight="true">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -16583,7 +17054,7 @@
       <c r="AG435" s="1"/>
       <c r="AH435" s="1"/>
     </row>
-    <row r="436" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="436" ht="12.75" customHeight="true">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -16619,7 +17090,7 @@
       <c r="AG436" s="1"/>
       <c r="AH436" s="1"/>
     </row>
-    <row r="437" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="437" ht="12.75" customHeight="true">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -16655,7 +17126,7 @@
       <c r="AG437" s="1"/>
       <c r="AH437" s="1"/>
     </row>
-    <row r="438" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="438" ht="12.75" customHeight="true">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -16691,7 +17162,7 @@
       <c r="AG438" s="1"/>
       <c r="AH438" s="1"/>
     </row>
-    <row r="439" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="439" ht="12.75" customHeight="true">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -16727,7 +17198,7 @@
       <c r="AG439" s="1"/>
       <c r="AH439" s="1"/>
     </row>
-    <row r="440" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="440" ht="12.75" customHeight="true">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -16763,7 +17234,7 @@
       <c r="AG440" s="1"/>
       <c r="AH440" s="1"/>
     </row>
-    <row r="441" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="441" ht="12.75" customHeight="true">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -16799,7 +17270,7 @@
       <c r="AG441" s="1"/>
       <c r="AH441" s="1"/>
     </row>
-    <row r="442" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="442" ht="12.75" customHeight="true">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -16835,7 +17306,7 @@
       <c r="AG442" s="1"/>
       <c r="AH442" s="1"/>
     </row>
-    <row r="443" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="443" ht="12.75" customHeight="true">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -16871,7 +17342,7 @@
       <c r="AG443" s="1"/>
       <c r="AH443" s="1"/>
     </row>
-    <row r="444" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="444" ht="12.75" customHeight="true">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -16907,7 +17378,7 @@
       <c r="AG444" s="1"/>
       <c r="AH444" s="1"/>
     </row>
-    <row r="445" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="445" ht="12.75" customHeight="true">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -16943,7 +17414,7 @@
       <c r="AG445" s="1"/>
       <c r="AH445" s="1"/>
     </row>
-    <row r="446" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="446" ht="12.75" customHeight="true">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -16979,7 +17450,7 @@
       <c r="AG446" s="1"/>
       <c r="AH446" s="1"/>
     </row>
-    <row r="447" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="447" ht="12.75" customHeight="true">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -17015,7 +17486,7 @@
       <c r="AG447" s="1"/>
       <c r="AH447" s="1"/>
     </row>
-    <row r="448" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="448" ht="12.75" customHeight="true">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -17051,7 +17522,7 @@
       <c r="AG448" s="1"/>
       <c r="AH448" s="1"/>
     </row>
-    <row r="449" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="449" ht="12.75" customHeight="true">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -17087,7 +17558,7 @@
       <c r="AG449" s="1"/>
       <c r="AH449" s="1"/>
     </row>
-    <row r="450" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="450" ht="12.75" customHeight="true">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -17123,7 +17594,7 @@
       <c r="AG450" s="1"/>
       <c r="AH450" s="1"/>
     </row>
-    <row r="451" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="451" ht="12.75" customHeight="true">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -17159,7 +17630,7 @@
       <c r="AG451" s="1"/>
       <c r="AH451" s="1"/>
     </row>
-    <row r="452" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="452" ht="12.75" customHeight="true">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -17195,7 +17666,7 @@
       <c r="AG452" s="1"/>
       <c r="AH452" s="1"/>
     </row>
-    <row r="453" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="453" ht="12.75" customHeight="true">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -17231,7 +17702,7 @@
       <c r="AG453" s="1"/>
       <c r="AH453" s="1"/>
     </row>
-    <row r="454" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="454" ht="12.75" customHeight="true">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -17267,7 +17738,7 @@
       <c r="AG454" s="1"/>
       <c r="AH454" s="1"/>
     </row>
-    <row r="455" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="455" ht="12.75" customHeight="true">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -17303,7 +17774,7 @@
       <c r="AG455" s="1"/>
       <c r="AH455" s="1"/>
     </row>
-    <row r="456" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="456" ht="12.75" customHeight="true">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -17339,7 +17810,7 @@
       <c r="AG456" s="1"/>
       <c r="AH456" s="1"/>
     </row>
-    <row r="457" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="457" ht="12.75" customHeight="true">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -17375,7 +17846,7 @@
       <c r="AG457" s="1"/>
       <c r="AH457" s="1"/>
     </row>
-    <row r="458" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="458" ht="12.75" customHeight="true">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -17411,7 +17882,7 @@
       <c r="AG458" s="1"/>
       <c r="AH458" s="1"/>
     </row>
-    <row r="459" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="459" ht="12.75" customHeight="true">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -17447,7 +17918,7 @@
       <c r="AG459" s="1"/>
       <c r="AH459" s="1"/>
     </row>
-    <row r="460" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="460" ht="12.75" customHeight="true">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -17483,7 +17954,7 @@
       <c r="AG460" s="1"/>
       <c r="AH460" s="1"/>
     </row>
-    <row r="461" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="461" ht="12.75" customHeight="true">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -17519,7 +17990,7 @@
       <c r="AG461" s="1"/>
       <c r="AH461" s="1"/>
     </row>
-    <row r="462" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="462" ht="12.75" customHeight="true">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -17555,7 +18026,7 @@
       <c r="AG462" s="1"/>
       <c r="AH462" s="1"/>
     </row>
-    <row r="463" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="463" ht="12.75" customHeight="true">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -17591,7 +18062,7 @@
       <c r="AG463" s="1"/>
       <c r="AH463" s="1"/>
     </row>
-    <row r="464" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="464" ht="12.75" customHeight="true">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -17627,7 +18098,7 @@
       <c r="AG464" s="1"/>
       <c r="AH464" s="1"/>
     </row>
-    <row r="465" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="465" ht="12.75" customHeight="true">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -17663,7 +18134,7 @@
       <c r="AG465" s="1"/>
       <c r="AH465" s="1"/>
     </row>
-    <row r="466" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="466" ht="12.75" customHeight="true">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -17699,7 +18170,7 @@
       <c r="AG466" s="1"/>
       <c r="AH466" s="1"/>
     </row>
-    <row r="467" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="467" ht="12.75" customHeight="true">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -17735,7 +18206,7 @@
       <c r="AG467" s="1"/>
       <c r="AH467" s="1"/>
     </row>
-    <row r="468" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="468" ht="12.75" customHeight="true">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -17771,7 +18242,7 @@
       <c r="AG468" s="1"/>
       <c r="AH468" s="1"/>
     </row>
-    <row r="469" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="469" ht="12.75" customHeight="true">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -17807,7 +18278,7 @@
       <c r="AG469" s="1"/>
       <c r="AH469" s="1"/>
     </row>
-    <row r="470" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="470" ht="12.75" customHeight="true">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -17843,7 +18314,7 @@
       <c r="AG470" s="1"/>
       <c r="AH470" s="1"/>
     </row>
-    <row r="471" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="471" ht="12.75" customHeight="true">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -17879,7 +18350,7 @@
       <c r="AG471" s="1"/>
       <c r="AH471" s="1"/>
     </row>
-    <row r="472" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="472" ht="12.75" customHeight="true">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -17915,7 +18386,7 @@
       <c r="AG472" s="1"/>
       <c r="AH472" s="1"/>
     </row>
-    <row r="473" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="473" ht="12.75" customHeight="true">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -17951,7 +18422,7 @@
       <c r="AG473" s="1"/>
       <c r="AH473" s="1"/>
     </row>
-    <row r="474" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="474" ht="12.75" customHeight="true">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -17987,7 +18458,7 @@
       <c r="AG474" s="1"/>
       <c r="AH474" s="1"/>
     </row>
-    <row r="475" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="475" ht="12.75" customHeight="true">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -18023,7 +18494,7 @@
       <c r="AG475" s="1"/>
       <c r="AH475" s="1"/>
     </row>
-    <row r="476" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="476" ht="12.75" customHeight="true">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -18059,7 +18530,7 @@
       <c r="AG476" s="1"/>
       <c r="AH476" s="1"/>
     </row>
-    <row r="477" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="477" ht="12.75" customHeight="true">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -18095,7 +18566,7 @@
       <c r="AG477" s="1"/>
       <c r="AH477" s="1"/>
     </row>
-    <row r="478" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="478" ht="12.75" customHeight="true">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -18131,7 +18602,7 @@
       <c r="AG478" s="1"/>
       <c r="AH478" s="1"/>
     </row>
-    <row r="479" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="479" ht="12.75" customHeight="true">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -18167,7 +18638,7 @@
       <c r="AG479" s="1"/>
       <c r="AH479" s="1"/>
     </row>
-    <row r="480" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="480" ht="12.75" customHeight="true">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -18203,7 +18674,7 @@
       <c r="AG480" s="1"/>
       <c r="AH480" s="1"/>
     </row>
-    <row r="481" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="481" ht="12.75" customHeight="true">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -18239,7 +18710,7 @@
       <c r="AG481" s="1"/>
       <c r="AH481" s="1"/>
     </row>
-    <row r="482" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="482" ht="12.75" customHeight="true">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -18275,7 +18746,7 @@
       <c r="AG482" s="1"/>
       <c r="AH482" s="1"/>
     </row>
-    <row r="483" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="483" ht="12.75" customHeight="true">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -18311,7 +18782,7 @@
       <c r="AG483" s="1"/>
       <c r="AH483" s="1"/>
     </row>
-    <row r="484" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="484" ht="12.75" customHeight="true">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -18347,7 +18818,7 @@
       <c r="AG484" s="1"/>
       <c r="AH484" s="1"/>
     </row>
-    <row r="485" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="485" ht="12.75" customHeight="true">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -18383,7 +18854,7 @@
       <c r="AG485" s="1"/>
       <c r="AH485" s="1"/>
     </row>
-    <row r="486" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="486" ht="12.75" customHeight="true">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -18419,7 +18890,7 @@
       <c r="AG486" s="1"/>
       <c r="AH486" s="1"/>
     </row>
-    <row r="487" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="487" ht="12.75" customHeight="true">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -18455,7 +18926,7 @@
       <c r="AG487" s="1"/>
       <c r="AH487" s="1"/>
     </row>
-    <row r="488" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="488" ht="12.75" customHeight="true">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -18491,7 +18962,7 @@
       <c r="AG488" s="1"/>
       <c r="AH488" s="1"/>
     </row>
-    <row r="489" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="489" ht="12.75" customHeight="true">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -18527,7 +18998,7 @@
       <c r="AG489" s="1"/>
       <c r="AH489" s="1"/>
     </row>
-    <row r="490" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="490" ht="12.75" customHeight="true">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -18563,7 +19034,7 @@
       <c r="AG490" s="1"/>
       <c r="AH490" s="1"/>
     </row>
-    <row r="491" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="491" ht="12.75" customHeight="true">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -18599,7 +19070,7 @@
       <c r="AG491" s="1"/>
       <c r="AH491" s="1"/>
     </row>
-    <row r="492" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="492" ht="12.75" customHeight="true">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -18635,7 +19106,7 @@
       <c r="AG492" s="1"/>
       <c r="AH492" s="1"/>
     </row>
-    <row r="493" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="493" ht="12.75" customHeight="true">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -18671,7 +19142,7 @@
       <c r="AG493" s="1"/>
       <c r="AH493" s="1"/>
     </row>
-    <row r="494" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="494" ht="12.75" customHeight="true">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -18707,7 +19178,7 @@
       <c r="AG494" s="1"/>
       <c r="AH494" s="1"/>
     </row>
-    <row r="495" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="495" ht="12.75" customHeight="true">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -18743,7 +19214,7 @@
       <c r="AG495" s="1"/>
       <c r="AH495" s="1"/>
     </row>
-    <row r="496" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="496" ht="12.75" customHeight="true">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -18779,7 +19250,7 @@
       <c r="AG496" s="1"/>
       <c r="AH496" s="1"/>
     </row>
-    <row r="497" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="497" ht="12.75" customHeight="true">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -18815,7 +19286,7 @@
       <c r="AG497" s="1"/>
       <c r="AH497" s="1"/>
     </row>
-    <row r="498" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="498" ht="12.75" customHeight="true">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -18851,7 +19322,7 @@
       <c r="AG498" s="1"/>
       <c r="AH498" s="1"/>
     </row>
-    <row r="499" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="499" ht="12.75" customHeight="true">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -18887,7 +19358,7 @@
       <c r="AG499" s="1"/>
       <c r="AH499" s="1"/>
     </row>
-    <row r="500" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="500" ht="12.75" customHeight="true">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -18923,7 +19394,7 @@
       <c r="AG500" s="1"/>
       <c r="AH500" s="1"/>
     </row>
-    <row r="501" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="501" ht="12.75" customHeight="true">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -18959,7 +19430,7 @@
       <c r="AG501" s="1"/>
       <c r="AH501" s="1"/>
     </row>
-    <row r="502" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="502" ht="12.75" customHeight="true">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -18995,7 +19466,7 @@
       <c r="AG502" s="1"/>
       <c r="AH502" s="1"/>
     </row>
-    <row r="503" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="503" ht="12.75" customHeight="true">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -19031,7 +19502,7 @@
       <c r="AG503" s="1"/>
       <c r="AH503" s="1"/>
     </row>
-    <row r="504" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="504" ht="12.75" customHeight="true">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -19067,7 +19538,7 @@
       <c r="AG504" s="1"/>
       <c r="AH504" s="1"/>
     </row>
-    <row r="505" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="505" ht="12.75" customHeight="true">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -19103,7 +19574,7 @@
       <c r="AG505" s="1"/>
       <c r="AH505" s="1"/>
     </row>
-    <row r="506" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="506" ht="12.75" customHeight="true">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -19139,7 +19610,7 @@
       <c r="AG506" s="1"/>
       <c r="AH506" s="1"/>
     </row>
-    <row r="507" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="507" ht="12.75" customHeight="true">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -19175,7 +19646,7 @@
       <c r="AG507" s="1"/>
       <c r="AH507" s="1"/>
     </row>
-    <row r="508" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="508" ht="12.75" customHeight="true">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -19211,7 +19682,7 @@
       <c r="AG508" s="1"/>
       <c r="AH508" s="1"/>
     </row>
-    <row r="509" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="509" ht="12.75" customHeight="true">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -19247,7 +19718,7 @@
       <c r="AG509" s="1"/>
       <c r="AH509" s="1"/>
     </row>
-    <row r="510" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="510" ht="12.75" customHeight="true">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -19283,7 +19754,7 @@
       <c r="AG510" s="1"/>
       <c r="AH510" s="1"/>
     </row>
-    <row r="511" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="511" ht="12.75" customHeight="true">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -19319,7 +19790,7 @@
       <c r="AG511" s="1"/>
       <c r="AH511" s="1"/>
     </row>
-    <row r="512" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="512" ht="12.75" customHeight="true">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -19355,7 +19826,7 @@
       <c r="AG512" s="1"/>
       <c r="AH512" s="1"/>
     </row>
-    <row r="513" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="513" ht="12.75" customHeight="true">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -19391,7 +19862,7 @@
       <c r="AG513" s="1"/>
       <c r="AH513" s="1"/>
     </row>
-    <row r="514" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="514" ht="12.75" customHeight="true">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -19427,7 +19898,7 @@
       <c r="AG514" s="1"/>
       <c r="AH514" s="1"/>
     </row>
-    <row r="515" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="515" ht="12.75" customHeight="true">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -19463,7 +19934,7 @@
       <c r="AG515" s="1"/>
       <c r="AH515" s="1"/>
     </row>
-    <row r="516" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="516" ht="12.75" customHeight="true">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -19499,7 +19970,7 @@
       <c r="AG516" s="1"/>
       <c r="AH516" s="1"/>
     </row>
-    <row r="517" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="517" ht="12.75" customHeight="true">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -19535,7 +20006,7 @@
       <c r="AG517" s="1"/>
       <c r="AH517" s="1"/>
     </row>
-    <row r="518" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="518" ht="12.75" customHeight="true">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -19571,7 +20042,7 @@
       <c r="AG518" s="1"/>
       <c r="AH518" s="1"/>
     </row>
-    <row r="519" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="519" ht="12.75" customHeight="true">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -19607,7 +20078,7 @@
       <c r="AG519" s="1"/>
       <c r="AH519" s="1"/>
     </row>
-    <row r="520" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="520" ht="12.75" customHeight="true">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -19643,7 +20114,7 @@
       <c r="AG520" s="1"/>
       <c r="AH520" s="1"/>
     </row>
-    <row r="521" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="521" ht="12.75" customHeight="true">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -19679,7 +20150,7 @@
       <c r="AG521" s="1"/>
       <c r="AH521" s="1"/>
     </row>
-    <row r="522" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="522" ht="12.75" customHeight="true">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -19715,7 +20186,7 @@
       <c r="AG522" s="1"/>
       <c r="AH522" s="1"/>
     </row>
-    <row r="523" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="523" ht="12.75" customHeight="true">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -19751,7 +20222,7 @@
       <c r="AG523" s="1"/>
       <c r="AH523" s="1"/>
     </row>
-    <row r="524" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="524" ht="12.75" customHeight="true">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -19787,7 +20258,7 @@
       <c r="AG524" s="1"/>
       <c r="AH524" s="1"/>
     </row>
-    <row r="525" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="525" ht="12.75" customHeight="true">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -19823,7 +20294,7 @@
       <c r="AG525" s="1"/>
       <c r="AH525" s="1"/>
     </row>
-    <row r="526" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="526" ht="12.75" customHeight="true">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -19859,7 +20330,7 @@
       <c r="AG526" s="1"/>
       <c r="AH526" s="1"/>
     </row>
-    <row r="527" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="527" ht="12.75" customHeight="true">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -19895,7 +20366,7 @@
       <c r="AG527" s="1"/>
       <c r="AH527" s="1"/>
     </row>
-    <row r="528" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="528" ht="12.75" customHeight="true">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -19931,7 +20402,7 @@
       <c r="AG528" s="1"/>
       <c r="AH528" s="1"/>
     </row>
-    <row r="529" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="529" ht="12.75" customHeight="true">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -19967,7 +20438,7 @@
       <c r="AG529" s="1"/>
       <c r="AH529" s="1"/>
     </row>
-    <row r="530" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="530" ht="12.75" customHeight="true">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -20003,7 +20474,7 @@
       <c r="AG530" s="1"/>
       <c r="AH530" s="1"/>
     </row>
-    <row r="531" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="531" ht="12.75" customHeight="true">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -20039,7 +20510,7 @@
       <c r="AG531" s="1"/>
       <c r="AH531" s="1"/>
     </row>
-    <row r="532" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="532" ht="12.75" customHeight="true">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -20075,7 +20546,7 @@
       <c r="AG532" s="1"/>
       <c r="AH532" s="1"/>
     </row>
-    <row r="533" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="533" ht="12.75" customHeight="true">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -20111,7 +20582,7 @@
       <c r="AG533" s="1"/>
       <c r="AH533" s="1"/>
     </row>
-    <row r="534" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="534" ht="12.75" customHeight="true">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -20147,7 +20618,7 @@
       <c r="AG534" s="1"/>
       <c r="AH534" s="1"/>
     </row>
-    <row r="535" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="535" ht="12.75" customHeight="true">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -20183,7 +20654,7 @@
       <c r="AG535" s="1"/>
       <c r="AH535" s="1"/>
     </row>
-    <row r="536" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="536" ht="12.75" customHeight="true">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -20219,7 +20690,7 @@
       <c r="AG536" s="1"/>
       <c r="AH536" s="1"/>
     </row>
-    <row r="537" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="537" ht="12.75" customHeight="true">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -20255,7 +20726,7 @@
       <c r="AG537" s="1"/>
       <c r="AH537" s="1"/>
     </row>
-    <row r="538" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="538" ht="12.75" customHeight="true">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -20291,7 +20762,7 @@
       <c r="AG538" s="1"/>
       <c r="AH538" s="1"/>
     </row>
-    <row r="539" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="539" ht="12.75" customHeight="true">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -20327,7 +20798,7 @@
       <c r="AG539" s="1"/>
       <c r="AH539" s="1"/>
     </row>
-    <row r="540" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="540" ht="12.75" customHeight="true">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -20363,7 +20834,7 @@
       <c r="AG540" s="1"/>
       <c r="AH540" s="1"/>
     </row>
-    <row r="541" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="541" ht="12.75" customHeight="true">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -20399,7 +20870,7 @@
       <c r="AG541" s="1"/>
       <c r="AH541" s="1"/>
     </row>
-    <row r="542" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="542" ht="12.75" customHeight="true">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -20435,7 +20906,7 @@
       <c r="AG542" s="1"/>
       <c r="AH542" s="1"/>
     </row>
-    <row r="543" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="543" ht="12.75" customHeight="true">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -20471,7 +20942,7 @@
       <c r="AG543" s="1"/>
       <c r="AH543" s="1"/>
     </row>
-    <row r="544" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="544" ht="12.75" customHeight="true">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -20507,7 +20978,7 @@
       <c r="AG544" s="1"/>
       <c r="AH544" s="1"/>
     </row>
-    <row r="545" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="545" ht="12.75" customHeight="true">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -20543,7 +21014,7 @@
       <c r="AG545" s="1"/>
       <c r="AH545" s="1"/>
     </row>
-    <row r="546" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="546" ht="12.75" customHeight="true">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -20579,7 +21050,7 @@
       <c r="AG546" s="1"/>
       <c r="AH546" s="1"/>
     </row>
-    <row r="547" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="547" ht="12.75" customHeight="true">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -20615,7 +21086,7 @@
       <c r="AG547" s="1"/>
       <c r="AH547" s="1"/>
     </row>
-    <row r="548" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="548" ht="12.75" customHeight="true">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -20651,7 +21122,7 @@
       <c r="AG548" s="1"/>
       <c r="AH548" s="1"/>
     </row>
-    <row r="549" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="549" ht="12.75" customHeight="true">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -20687,7 +21158,7 @@
       <c r="AG549" s="1"/>
       <c r="AH549" s="1"/>
     </row>
-    <row r="550" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="550" ht="12.75" customHeight="true">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -20723,7 +21194,7 @@
       <c r="AG550" s="1"/>
       <c r="AH550" s="1"/>
     </row>
-    <row r="551" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="551" ht="12.75" customHeight="true">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -20759,7 +21230,7 @@
       <c r="AG551" s="1"/>
       <c r="AH551" s="1"/>
     </row>
-    <row r="552" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="552" ht="12.75" customHeight="true">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -20795,7 +21266,7 @@
       <c r="AG552" s="1"/>
       <c r="AH552" s="1"/>
     </row>
-    <row r="553" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="553" ht="12.75" customHeight="true">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -20831,7 +21302,7 @@
       <c r="AG553" s="1"/>
       <c r="AH553" s="1"/>
     </row>
-    <row r="554" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="554" ht="12.75" customHeight="true">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -20867,7 +21338,7 @@
       <c r="AG554" s="1"/>
       <c r="AH554" s="1"/>
     </row>
-    <row r="555" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="555" ht="12.75" customHeight="true">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -20903,7 +21374,7 @@
       <c r="AG555" s="1"/>
       <c r="AH555" s="1"/>
     </row>
-    <row r="556" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="556" ht="12.75" customHeight="true">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -20939,7 +21410,7 @@
       <c r="AG556" s="1"/>
       <c r="AH556" s="1"/>
     </row>
-    <row r="557" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="557" ht="12.75" customHeight="true">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -20975,7 +21446,7 @@
       <c r="AG557" s="1"/>
       <c r="AH557" s="1"/>
     </row>
-    <row r="558" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="558" ht="12.75" customHeight="true">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -21011,7 +21482,7 @@
       <c r="AG558" s="1"/>
       <c r="AH558" s="1"/>
     </row>
-    <row r="559" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="559" ht="12.75" customHeight="true">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -21047,7 +21518,7 @@
       <c r="AG559" s="1"/>
       <c r="AH559" s="1"/>
     </row>
-    <row r="560" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="560" ht="12.75" customHeight="true">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -21083,7 +21554,7 @@
       <c r="AG560" s="1"/>
       <c r="AH560" s="1"/>
     </row>
-    <row r="561" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="561" ht="12.75" customHeight="true">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -21119,7 +21590,7 @@
       <c r="AG561" s="1"/>
       <c r="AH561" s="1"/>
     </row>
-    <row r="562" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="562" ht="12.75" customHeight="true">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -21155,7 +21626,7 @@
       <c r="AG562" s="1"/>
       <c r="AH562" s="1"/>
     </row>
-    <row r="563" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="563" ht="12.75" customHeight="true">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -21191,7 +21662,7 @@
       <c r="AG563" s="1"/>
       <c r="AH563" s="1"/>
     </row>
-    <row r="564" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="564" ht="12.75" customHeight="true">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -21227,7 +21698,7 @@
       <c r="AG564" s="1"/>
       <c r="AH564" s="1"/>
     </row>
-    <row r="565" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="565" ht="12.75" customHeight="true">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -21263,7 +21734,7 @@
       <c r="AG565" s="1"/>
       <c r="AH565" s="1"/>
     </row>
-    <row r="566" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="566" ht="12.75" customHeight="true">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -21299,7 +21770,7 @@
       <c r="AG566" s="1"/>
       <c r="AH566" s="1"/>
     </row>
-    <row r="567" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="567" ht="12.75" customHeight="true">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -21335,7 +21806,7 @@
       <c r="AG567" s="1"/>
       <c r="AH567" s="1"/>
     </row>
-    <row r="568" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="568" ht="12.75" customHeight="true">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -21371,7 +21842,7 @@
       <c r="AG568" s="1"/>
       <c r="AH568" s="1"/>
     </row>
-    <row r="569" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="569" ht="12.75" customHeight="true">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -21407,7 +21878,7 @@
       <c r="AG569" s="1"/>
       <c r="AH569" s="1"/>
     </row>
-    <row r="570" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="570" ht="12.75" customHeight="true">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -21443,7 +21914,7 @@
       <c r="AG570" s="1"/>
       <c r="AH570" s="1"/>
     </row>
-    <row r="571" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="571" ht="12.75" customHeight="true">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -21479,7 +21950,7 @@
       <c r="AG571" s="1"/>
       <c r="AH571" s="1"/>
     </row>
-    <row r="572" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="572" ht="12.75" customHeight="true">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -21515,7 +21986,7 @@
       <c r="AG572" s="1"/>
       <c r="AH572" s="1"/>
     </row>
-    <row r="573" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="573" ht="12.75" customHeight="true">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -21551,7 +22022,7 @@
       <c r="AG573" s="1"/>
       <c r="AH573" s="1"/>
     </row>
-    <row r="574" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="574" ht="12.75" customHeight="true">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -21587,7 +22058,7 @@
       <c r="AG574" s="1"/>
       <c r="AH574" s="1"/>
     </row>
-    <row r="575" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="575" ht="12.75" customHeight="true">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -21623,7 +22094,7 @@
       <c r="AG575" s="1"/>
       <c r="AH575" s="1"/>
     </row>
-    <row r="576" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="576" ht="12.75" customHeight="true">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -21659,7 +22130,7 @@
       <c r="AG576" s="1"/>
       <c r="AH576" s="1"/>
     </row>
-    <row r="577" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="577" ht="12.75" customHeight="true">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -21695,7 +22166,7 @@
       <c r="AG577" s="1"/>
       <c r="AH577" s="1"/>
     </row>
-    <row r="578" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="578" ht="12.75" customHeight="true">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -21731,7 +22202,7 @@
       <c r="AG578" s="1"/>
       <c r="AH578" s="1"/>
     </row>
-    <row r="579" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="579" ht="12.75" customHeight="true">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -21767,7 +22238,7 @@
       <c r="AG579" s="1"/>
       <c r="AH579" s="1"/>
     </row>
-    <row r="580" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="580" ht="12.75" customHeight="true">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -21803,7 +22274,7 @@
       <c r="AG580" s="1"/>
       <c r="AH580" s="1"/>
     </row>
-    <row r="581" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="581" ht="12.75" customHeight="true">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -21839,7 +22310,7 @@
       <c r="AG581" s="1"/>
       <c r="AH581" s="1"/>
     </row>
-    <row r="582" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="582" ht="12.75" customHeight="true">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -21875,7 +22346,7 @@
       <c r="AG582" s="1"/>
       <c r="AH582" s="1"/>
     </row>
-    <row r="583" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="583" ht="12.75" customHeight="true">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -21911,7 +22382,7 @@
       <c r="AG583" s="1"/>
       <c r="AH583" s="1"/>
     </row>
-    <row r="584" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="584" ht="12.75" customHeight="true">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -21947,7 +22418,7 @@
       <c r="AG584" s="1"/>
       <c r="AH584" s="1"/>
     </row>
-    <row r="585" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="585" ht="12.75" customHeight="true">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -21983,7 +22454,7 @@
       <c r="AG585" s="1"/>
       <c r="AH585" s="1"/>
     </row>
-    <row r="586" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="586" ht="12.75" customHeight="true">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -22019,7 +22490,7 @@
       <c r="AG586" s="1"/>
       <c r="AH586" s="1"/>
     </row>
-    <row r="587" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="587" ht="12.75" customHeight="true">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -22055,7 +22526,7 @@
       <c r="AG587" s="1"/>
       <c r="AH587" s="1"/>
     </row>
-    <row r="588" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="588" ht="12.75" customHeight="true">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -22091,7 +22562,7 @@
       <c r="AG588" s="1"/>
       <c r="AH588" s="1"/>
     </row>
-    <row r="589" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="589" ht="12.75" customHeight="true">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -22127,7 +22598,7 @@
       <c r="AG589" s="1"/>
       <c r="AH589" s="1"/>
     </row>
-    <row r="590" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="590" ht="12.75" customHeight="true">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -22163,7 +22634,7 @@
       <c r="AG590" s="1"/>
       <c r="AH590" s="1"/>
     </row>
-    <row r="591" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="591" ht="12.75" customHeight="true">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -22199,7 +22670,7 @@
       <c r="AG591" s="1"/>
       <c r="AH591" s="1"/>
     </row>
-    <row r="592" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="592" ht="12.75" customHeight="true">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -22235,7 +22706,7 @@
       <c r="AG592" s="1"/>
       <c r="AH592" s="1"/>
     </row>
-    <row r="593" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="593" ht="12.75" customHeight="true">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -22271,7 +22742,7 @@
       <c r="AG593" s="1"/>
       <c r="AH593" s="1"/>
     </row>
-    <row r="594" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="594" ht="12.75" customHeight="true">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -22307,7 +22778,7 @@
       <c r="AG594" s="1"/>
       <c r="AH594" s="1"/>
     </row>
-    <row r="595" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="595" ht="12.75" customHeight="true">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -22343,7 +22814,7 @@
       <c r="AG595" s="1"/>
       <c r="AH595" s="1"/>
     </row>
-    <row r="596" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="596" ht="12.75" customHeight="true">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -22379,7 +22850,7 @@
       <c r="AG596" s="1"/>
       <c r="AH596" s="1"/>
     </row>
-    <row r="597" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="597" ht="12.75" customHeight="true">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -22415,7 +22886,7 @@
       <c r="AG597" s="1"/>
       <c r="AH597" s="1"/>
     </row>
-    <row r="598" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="598" ht="12.75" customHeight="true">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -22451,7 +22922,7 @@
       <c r="AG598" s="1"/>
       <c r="AH598" s="1"/>
     </row>
-    <row r="599" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="599" ht="12.75" customHeight="true">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -22487,7 +22958,7 @@
       <c r="AG599" s="1"/>
       <c r="AH599" s="1"/>
     </row>
-    <row r="600" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="600" ht="12.75" customHeight="true">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -22523,7 +22994,7 @@
       <c r="AG600" s="1"/>
       <c r="AH600" s="1"/>
     </row>
-    <row r="601" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="601" ht="12.75" customHeight="true">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -22559,7 +23030,7 @@
       <c r="AG601" s="1"/>
       <c r="AH601" s="1"/>
     </row>
-    <row r="602" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="602" ht="12.75" customHeight="true">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -22595,7 +23066,7 @@
       <c r="AG602" s="1"/>
       <c r="AH602" s="1"/>
     </row>
-    <row r="603" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="603" ht="12.75" customHeight="true">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -22631,7 +23102,7 @@
       <c r="AG603" s="1"/>
       <c r="AH603" s="1"/>
     </row>
-    <row r="604" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="604" ht="12.75" customHeight="true">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -22667,7 +23138,7 @@
       <c r="AG604" s="1"/>
       <c r="AH604" s="1"/>
     </row>
-    <row r="605" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="605" ht="12.75" customHeight="true">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -22703,7 +23174,7 @@
       <c r="AG605" s="1"/>
       <c r="AH605" s="1"/>
     </row>
-    <row r="606" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="606" ht="12.75" customHeight="true">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -22739,7 +23210,7 @@
       <c r="AG606" s="1"/>
       <c r="AH606" s="1"/>
     </row>
-    <row r="607" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="607" ht="12.75" customHeight="true">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -22775,7 +23246,7 @@
       <c r="AG607" s="1"/>
       <c r="AH607" s="1"/>
     </row>
-    <row r="608" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="608" ht="12.75" customHeight="true">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -22811,7 +23282,7 @@
       <c r="AG608" s="1"/>
       <c r="AH608" s="1"/>
     </row>
-    <row r="609" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="609" ht="12.75" customHeight="true">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -22847,7 +23318,7 @@
       <c r="AG609" s="1"/>
       <c r="AH609" s="1"/>
     </row>
-    <row r="610" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="610" ht="12.75" customHeight="true">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -22883,7 +23354,7 @@
       <c r="AG610" s="1"/>
       <c r="AH610" s="1"/>
     </row>
-    <row r="611" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="611" ht="12.75" customHeight="true">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -22919,7 +23390,7 @@
       <c r="AG611" s="1"/>
       <c r="AH611" s="1"/>
     </row>
-    <row r="612" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="612" ht="12.75" customHeight="true">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -22955,7 +23426,7 @@
       <c r="AG612" s="1"/>
       <c r="AH612" s="1"/>
     </row>
-    <row r="613" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="613" ht="12.75" customHeight="true">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -22991,7 +23462,7 @@
       <c r="AG613" s="1"/>
       <c r="AH613" s="1"/>
     </row>
-    <row r="614" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="614" ht="12.75" customHeight="true">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -23027,7 +23498,7 @@
       <c r="AG614" s="1"/>
       <c r="AH614" s="1"/>
     </row>
-    <row r="615" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="615" ht="12.75" customHeight="true">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -23063,7 +23534,7 @@
       <c r="AG615" s="1"/>
       <c r="AH615" s="1"/>
     </row>
-    <row r="616" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="616" ht="12.75" customHeight="true">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -23099,7 +23570,7 @@
       <c r="AG616" s="1"/>
       <c r="AH616" s="1"/>
     </row>
-    <row r="617" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="617" ht="12.75" customHeight="true">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -23135,7 +23606,7 @@
       <c r="AG617" s="1"/>
       <c r="AH617" s="1"/>
     </row>
-    <row r="618" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="618" ht="12.75" customHeight="true">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -23171,7 +23642,7 @@
       <c r="AG618" s="1"/>
       <c r="AH618" s="1"/>
     </row>
-    <row r="619" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="619" ht="12.75" customHeight="true">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -23207,7 +23678,7 @@
       <c r="AG619" s="1"/>
       <c r="AH619" s="1"/>
     </row>
-    <row r="620" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="620" ht="12.75" customHeight="true">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -23243,7 +23714,7 @@
       <c r="AG620" s="1"/>
       <c r="AH620" s="1"/>
     </row>
-    <row r="621" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="621" ht="12.75" customHeight="true">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -23279,7 +23750,7 @@
       <c r="AG621" s="1"/>
       <c r="AH621" s="1"/>
     </row>
-    <row r="622" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="622" ht="12.75" customHeight="true">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -23315,7 +23786,7 @@
       <c r="AG622" s="1"/>
       <c r="AH622" s="1"/>
     </row>
-    <row r="623" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="623" ht="12.75" customHeight="true">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -23351,7 +23822,7 @@
       <c r="AG623" s="1"/>
       <c r="AH623" s="1"/>
     </row>
-    <row r="624" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="624" ht="12.75" customHeight="true">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -23387,7 +23858,7 @@
       <c r="AG624" s="1"/>
       <c r="AH624" s="1"/>
     </row>
-    <row r="625" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="625" ht="12.75" customHeight="true">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -23423,7 +23894,7 @@
       <c r="AG625" s="1"/>
       <c r="AH625" s="1"/>
     </row>
-    <row r="626" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="626" ht="12.75" customHeight="true">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -23459,7 +23930,7 @@
       <c r="AG626" s="1"/>
       <c r="AH626" s="1"/>
     </row>
-    <row r="627" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="627" ht="12.75" customHeight="true">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -23495,7 +23966,7 @@
       <c r="AG627" s="1"/>
       <c r="AH627" s="1"/>
     </row>
-    <row r="628" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="628" ht="12.75" customHeight="true">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -23531,7 +24002,7 @@
       <c r="AG628" s="1"/>
       <c r="AH628" s="1"/>
     </row>
-    <row r="629" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="629" ht="12.75" customHeight="true">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -23567,7 +24038,7 @@
       <c r="AG629" s="1"/>
       <c r="AH629" s="1"/>
     </row>
-    <row r="630" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="630" ht="12.75" customHeight="true">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -23603,7 +24074,7 @@
       <c r="AG630" s="1"/>
       <c r="AH630" s="1"/>
     </row>
-    <row r="631" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="631" ht="12.75" customHeight="true">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -23639,7 +24110,7 @@
       <c r="AG631" s="1"/>
       <c r="AH631" s="1"/>
     </row>
-    <row r="632" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="632" ht="12.75" customHeight="true">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -23675,7 +24146,7 @@
       <c r="AG632" s="1"/>
       <c r="AH632" s="1"/>
     </row>
-    <row r="633" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="633" ht="12.75" customHeight="true">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -23711,7 +24182,7 @@
       <c r="AG633" s="1"/>
       <c r="AH633" s="1"/>
     </row>
-    <row r="634" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="634" ht="12.75" customHeight="true">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -23747,7 +24218,7 @@
       <c r="AG634" s="1"/>
       <c r="AH634" s="1"/>
     </row>
-    <row r="635" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="635" ht="12.75" customHeight="true">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -23783,7 +24254,7 @@
       <c r="AG635" s="1"/>
       <c r="AH635" s="1"/>
     </row>
-    <row r="636" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="636" ht="12.75" customHeight="true">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -23819,7 +24290,7 @@
       <c r="AG636" s="1"/>
       <c r="AH636" s="1"/>
     </row>
-    <row r="637" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="637" ht="12.75" customHeight="true">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -23855,7 +24326,7 @@
       <c r="AG637" s="1"/>
       <c r="AH637" s="1"/>
     </row>
-    <row r="638" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="638" ht="12.75" customHeight="true">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -23891,7 +24362,7 @@
       <c r="AG638" s="1"/>
       <c r="AH638" s="1"/>
     </row>
-    <row r="639" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="639" ht="12.75" customHeight="true">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -23927,7 +24398,7 @@
       <c r="AG639" s="1"/>
       <c r="AH639" s="1"/>
     </row>
-    <row r="640" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="640" ht="12.75" customHeight="true">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -23963,7 +24434,7 @@
       <c r="AG640" s="1"/>
       <c r="AH640" s="1"/>
     </row>
-    <row r="641" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="641" ht="12.75" customHeight="true">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -23999,7 +24470,7 @@
       <c r="AG641" s="1"/>
       <c r="AH641" s="1"/>
     </row>
-    <row r="642" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="642" ht="12.75" customHeight="true">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -24035,7 +24506,7 @@
       <c r="AG642" s="1"/>
       <c r="AH642" s="1"/>
     </row>
-    <row r="643" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="643" ht="12.75" customHeight="true">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -24071,7 +24542,7 @@
       <c r="AG643" s="1"/>
       <c r="AH643" s="1"/>
     </row>
-    <row r="644" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="644" ht="12.75" customHeight="true">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -24107,7 +24578,7 @@
       <c r="AG644" s="1"/>
       <c r="AH644" s="1"/>
     </row>
-    <row r="645" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="645" ht="12.75" customHeight="true">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -24143,7 +24614,7 @@
       <c r="AG645" s="1"/>
       <c r="AH645" s="1"/>
     </row>
-    <row r="646" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="646" ht="12.75" customHeight="true">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -24179,7 +24650,7 @@
       <c r="AG646" s="1"/>
       <c r="AH646" s="1"/>
     </row>
-    <row r="647" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="647" ht="12.75" customHeight="true">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -24215,7 +24686,7 @@
       <c r="AG647" s="1"/>
       <c r="AH647" s="1"/>
     </row>
-    <row r="648" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="648" ht="12.75" customHeight="true">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -24251,7 +24722,7 @@
       <c r="AG648" s="1"/>
       <c r="AH648" s="1"/>
     </row>
-    <row r="649" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="649" ht="12.75" customHeight="true">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -24287,7 +24758,7 @@
       <c r="AG649" s="1"/>
       <c r="AH649" s="1"/>
     </row>
-    <row r="650" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="650" ht="12.75" customHeight="true">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -24323,7 +24794,7 @@
       <c r="AG650" s="1"/>
       <c r="AH650" s="1"/>
     </row>
-    <row r="651" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="651" ht="12.75" customHeight="true">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -24359,7 +24830,7 @@
       <c r="AG651" s="1"/>
       <c r="AH651" s="1"/>
     </row>
-    <row r="652" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="652" ht="12.75" customHeight="true">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -24395,7 +24866,7 @@
       <c r="AG652" s="1"/>
       <c r="AH652" s="1"/>
     </row>
-    <row r="653" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="653" ht="12.75" customHeight="true">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -24431,7 +24902,7 @@
       <c r="AG653" s="1"/>
       <c r="AH653" s="1"/>
     </row>
-    <row r="654" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="654" ht="12.75" customHeight="true">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -24467,7 +24938,7 @@
       <c r="AG654" s="1"/>
       <c r="AH654" s="1"/>
     </row>
-    <row r="655" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="655" ht="12.75" customHeight="true">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -24503,7 +24974,7 @@
       <c r="AG655" s="1"/>
       <c r="AH655" s="1"/>
     </row>
-    <row r="656" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="656" ht="12.75" customHeight="true">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -24539,7 +25010,7 @@
       <c r="AG656" s="1"/>
       <c r="AH656" s="1"/>
     </row>
-    <row r="657" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="657" ht="12.75" customHeight="true">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -24575,7 +25046,7 @@
       <c r="AG657" s="1"/>
       <c r="AH657" s="1"/>
     </row>
-    <row r="658" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="658" ht="12.75" customHeight="true">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -24611,7 +25082,7 @@
       <c r="AG658" s="1"/>
       <c r="AH658" s="1"/>
     </row>
-    <row r="659" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="659" ht="12.75" customHeight="true">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -24647,7 +25118,7 @@
       <c r="AG659" s="1"/>
       <c r="AH659" s="1"/>
     </row>
-    <row r="660" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="660" ht="12.75" customHeight="true">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -24683,7 +25154,7 @@
       <c r="AG660" s="1"/>
       <c r="AH660" s="1"/>
     </row>
-    <row r="661" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="661" ht="12.75" customHeight="true">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -24719,7 +25190,7 @@
       <c r="AG661" s="1"/>
       <c r="AH661" s="1"/>
     </row>
-    <row r="662" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="662" ht="12.75" customHeight="true">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -24755,7 +25226,7 @@
       <c r="AG662" s="1"/>
       <c r="AH662" s="1"/>
     </row>
-    <row r="663" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="663" ht="12.75" customHeight="true">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -24791,7 +25262,7 @@
       <c r="AG663" s="1"/>
       <c r="AH663" s="1"/>
     </row>
-    <row r="664" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="664" ht="12.75" customHeight="true">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -24827,7 +25298,7 @@
       <c r="AG664" s="1"/>
       <c r="AH664" s="1"/>
     </row>
-    <row r="665" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="665" ht="12.75" customHeight="true">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -24863,7 +25334,7 @@
       <c r="AG665" s="1"/>
       <c r="AH665" s="1"/>
     </row>
-    <row r="666" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="666" ht="12.75" customHeight="true">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -24899,7 +25370,7 @@
       <c r="AG666" s="1"/>
       <c r="AH666" s="1"/>
     </row>
-    <row r="667" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="667" ht="12.75" customHeight="true">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -24935,7 +25406,7 @@
       <c r="AG667" s="1"/>
       <c r="AH667" s="1"/>
     </row>
-    <row r="668" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="668" ht="12.75" customHeight="true">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -24971,7 +25442,7 @@
       <c r="AG668" s="1"/>
       <c r="AH668" s="1"/>
     </row>
-    <row r="669" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="669" ht="12.75" customHeight="true">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -25007,7 +25478,7 @@
       <c r="AG669" s="1"/>
       <c r="AH669" s="1"/>
     </row>
-    <row r="670" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="670" ht="12.75" customHeight="true">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -25043,7 +25514,7 @@
       <c r="AG670" s="1"/>
       <c r="AH670" s="1"/>
     </row>
-    <row r="671" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="671" ht="12.75" customHeight="true">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -25079,7 +25550,7 @@
       <c r="AG671" s="1"/>
       <c r="AH671" s="1"/>
     </row>
-    <row r="672" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="672" ht="12.75" customHeight="true">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -25115,7 +25586,7 @@
       <c r="AG672" s="1"/>
       <c r="AH672" s="1"/>
     </row>
-    <row r="673" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="673" ht="12.75" customHeight="true">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -25151,7 +25622,7 @@
       <c r="AG673" s="1"/>
       <c r="AH673" s="1"/>
     </row>
-    <row r="674" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="674" ht="12.75" customHeight="true">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -25187,7 +25658,7 @@
       <c r="AG674" s="1"/>
       <c r="AH674" s="1"/>
     </row>
-    <row r="675" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="675" ht="12.75" customHeight="true">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -25223,7 +25694,7 @@
       <c r="AG675" s="1"/>
       <c r="AH675" s="1"/>
     </row>
-    <row r="676" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="676" ht="12.75" customHeight="true">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -25259,7 +25730,7 @@
       <c r="AG676" s="1"/>
       <c r="AH676" s="1"/>
     </row>
-    <row r="677" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="677" ht="12.75" customHeight="true">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -25295,7 +25766,7 @@
       <c r="AG677" s="1"/>
       <c r="AH677" s="1"/>
     </row>
-    <row r="678" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="678" ht="12.75" customHeight="true">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -25331,7 +25802,7 @@
       <c r="AG678" s="1"/>
       <c r="AH678" s="1"/>
     </row>
-    <row r="679" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="679" ht="12.75" customHeight="true">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -25367,7 +25838,7 @@
       <c r="AG679" s="1"/>
       <c r="AH679" s="1"/>
     </row>
-    <row r="680" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="680" ht="12.75" customHeight="true">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -25403,7 +25874,7 @@
       <c r="AG680" s="1"/>
       <c r="AH680" s="1"/>
     </row>
-    <row r="681" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="681" ht="12.75" customHeight="true">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -25439,7 +25910,7 @@
       <c r="AG681" s="1"/>
       <c r="AH681" s="1"/>
     </row>
-    <row r="682" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="682" ht="12.75" customHeight="true">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -25475,7 +25946,7 @@
       <c r="AG682" s="1"/>
       <c r="AH682" s="1"/>
     </row>
-    <row r="683" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="683" ht="12.75" customHeight="true">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -25511,7 +25982,7 @@
       <c r="AG683" s="1"/>
       <c r="AH683" s="1"/>
     </row>
-    <row r="684" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="684" ht="12.75" customHeight="true">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -25547,7 +26018,7 @@
       <c r="AG684" s="1"/>
       <c r="AH684" s="1"/>
     </row>
-    <row r="685" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="685" ht="12.75" customHeight="true">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -25583,7 +26054,7 @@
       <c r="AG685" s="1"/>
       <c r="AH685" s="1"/>
     </row>
-    <row r="686" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="686" ht="12.75" customHeight="true">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -25619,7 +26090,7 @@
       <c r="AG686" s="1"/>
       <c r="AH686" s="1"/>
     </row>
-    <row r="687" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="687" ht="12.75" customHeight="true">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -25655,7 +26126,7 @@
       <c r="AG687" s="1"/>
       <c r="AH687" s="1"/>
     </row>
-    <row r="688" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="688" ht="12.75" customHeight="true">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -25691,7 +26162,7 @@
       <c r="AG688" s="1"/>
       <c r="AH688" s="1"/>
     </row>
-    <row r="689" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="689" ht="12.75" customHeight="true">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -25727,7 +26198,7 @@
       <c r="AG689" s="1"/>
       <c r="AH689" s="1"/>
     </row>
-    <row r="690" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="690" ht="12.75" customHeight="true">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -25763,7 +26234,7 @@
       <c r="AG690" s="1"/>
       <c r="AH690" s="1"/>
     </row>
-    <row r="691" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="691" ht="12.75" customHeight="true">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -25799,7 +26270,7 @@
       <c r="AG691" s="1"/>
       <c r="AH691" s="1"/>
     </row>
-    <row r="692" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="692" ht="12.75" customHeight="true">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -25835,7 +26306,7 @@
       <c r="AG692" s="1"/>
       <c r="AH692" s="1"/>
     </row>
-    <row r="693" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="693" ht="12.75" customHeight="true">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -25871,7 +26342,7 @@
       <c r="AG693" s="1"/>
       <c r="AH693" s="1"/>
     </row>
-    <row r="694" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="694" ht="12.75" customHeight="true">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -25907,7 +26378,7 @@
       <c r="AG694" s="1"/>
       <c r="AH694" s="1"/>
     </row>
-    <row r="695" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="695" ht="12.75" customHeight="true">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -25943,7 +26414,7 @@
       <c r="AG695" s="1"/>
       <c r="AH695" s="1"/>
     </row>
-    <row r="696" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="696" ht="12.75" customHeight="true">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -25979,7 +26450,7 @@
       <c r="AG696" s="1"/>
       <c r="AH696" s="1"/>
     </row>
-    <row r="697" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="697" ht="12.75" customHeight="true">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -26015,7 +26486,7 @@
       <c r="AG697" s="1"/>
       <c r="AH697" s="1"/>
     </row>
-    <row r="698" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="698" ht="12.75" customHeight="true">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -26051,7 +26522,7 @@
       <c r="AG698" s="1"/>
       <c r="AH698" s="1"/>
     </row>
-    <row r="699" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="699" ht="12.75" customHeight="true">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -26087,7 +26558,7 @@
       <c r="AG699" s="1"/>
       <c r="AH699" s="1"/>
     </row>
-    <row r="700" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="700" ht="12.75" customHeight="true">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -26123,7 +26594,7 @@
       <c r="AG700" s="1"/>
       <c r="AH700" s="1"/>
     </row>
-    <row r="701" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="701" ht="12.75" customHeight="true">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -26159,7 +26630,7 @@
       <c r="AG701" s="1"/>
       <c r="AH701" s="1"/>
     </row>
-    <row r="702" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="702" ht="12.75" customHeight="true">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -26195,7 +26666,7 @@
       <c r="AG702" s="1"/>
       <c r="AH702" s="1"/>
     </row>
-    <row r="703" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="703" ht="12.75" customHeight="true">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -26231,7 +26702,7 @@
       <c r="AG703" s="1"/>
       <c r="AH703" s="1"/>
     </row>
-    <row r="704" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="704" ht="12.75" customHeight="true">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -26267,7 +26738,7 @@
       <c r="AG704" s="1"/>
       <c r="AH704" s="1"/>
     </row>
-    <row r="705" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="705" ht="12.75" customHeight="true">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -26303,7 +26774,7 @@
       <c r="AG705" s="1"/>
       <c r="AH705" s="1"/>
     </row>
-    <row r="706" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="706" ht="12.75" customHeight="true">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -26339,7 +26810,7 @@
       <c r="AG706" s="1"/>
       <c r="AH706" s="1"/>
     </row>
-    <row r="707" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="707" ht="12.75" customHeight="true">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -26375,7 +26846,7 @@
       <c r="AG707" s="1"/>
       <c r="AH707" s="1"/>
     </row>
-    <row r="708" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="708" ht="12.75" customHeight="true">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -26411,7 +26882,7 @@
       <c r="AG708" s="1"/>
       <c r="AH708" s="1"/>
     </row>
-    <row r="709" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="709" ht="12.75" customHeight="true">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -26447,7 +26918,7 @@
       <c r="AG709" s="1"/>
       <c r="AH709" s="1"/>
     </row>
-    <row r="710" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="710" ht="12.75" customHeight="true">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -26483,7 +26954,7 @@
       <c r="AG710" s="1"/>
       <c r="AH710" s="1"/>
     </row>
-    <row r="711" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="711" ht="12.75" customHeight="true">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -26519,7 +26990,7 @@
       <c r="AG711" s="1"/>
       <c r="AH711" s="1"/>
     </row>
-    <row r="712" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="712" ht="12.75" customHeight="true">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -26555,7 +27026,7 @@
       <c r="AG712" s="1"/>
       <c r="AH712" s="1"/>
     </row>
-    <row r="713" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="713" ht="12.75" customHeight="true">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -26591,7 +27062,7 @@
       <c r="AG713" s="1"/>
       <c r="AH713" s="1"/>
     </row>
-    <row r="714" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="714" ht="12.75" customHeight="true">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -26627,7 +27098,7 @@
       <c r="AG714" s="1"/>
       <c r="AH714" s="1"/>
     </row>
-    <row r="715" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="715" ht="12.75" customHeight="true">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -26663,7 +27134,7 @@
       <c r="AG715" s="1"/>
       <c r="AH715" s="1"/>
     </row>
-    <row r="716" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="716" ht="12.75" customHeight="true">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -26699,7 +27170,7 @@
       <c r="AG716" s="1"/>
       <c r="AH716" s="1"/>
     </row>
-    <row r="717" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="717" ht="12.75" customHeight="true">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -26735,7 +27206,7 @@
       <c r="AG717" s="1"/>
       <c r="AH717" s="1"/>
     </row>
-    <row r="718" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="718" ht="12.75" customHeight="true">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -26771,7 +27242,7 @@
       <c r="AG718" s="1"/>
       <c r="AH718" s="1"/>
     </row>
-    <row r="719" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="719" ht="12.75" customHeight="true">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -26807,7 +27278,7 @@
       <c r="AG719" s="1"/>
       <c r="AH719" s="1"/>
     </row>
-    <row r="720" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="720" ht="12.75" customHeight="true">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -26843,7 +27314,7 @@
       <c r="AG720" s="1"/>
       <c r="AH720" s="1"/>
     </row>
-    <row r="721" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="721" ht="12.75" customHeight="true">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -26879,7 +27350,7 @@
       <c r="AG721" s="1"/>
       <c r="AH721" s="1"/>
     </row>
-    <row r="722" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="722" ht="12.75" customHeight="true">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -26915,7 +27386,7 @@
       <c r="AG722" s="1"/>
       <c r="AH722" s="1"/>
     </row>
-    <row r="723" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="723" ht="12.75" customHeight="true">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -26951,7 +27422,7 @@
       <c r="AG723" s="1"/>
       <c r="AH723" s="1"/>
     </row>
-    <row r="724" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="724" ht="12.75" customHeight="true">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -26987,7 +27458,7 @@
       <c r="AG724" s="1"/>
       <c r="AH724" s="1"/>
     </row>
-    <row r="725" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="725" ht="12.75" customHeight="true">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -27023,7 +27494,7 @@
       <c r="AG725" s="1"/>
       <c r="AH725" s="1"/>
     </row>
-    <row r="726" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="726" ht="12.75" customHeight="true">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -27059,7 +27530,7 @@
       <c r="AG726" s="1"/>
       <c r="AH726" s="1"/>
     </row>
-    <row r="727" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="727" ht="12.75" customHeight="true">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -27095,7 +27566,7 @@
       <c r="AG727" s="1"/>
       <c r="AH727" s="1"/>
     </row>
-    <row r="728" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="728" ht="12.75" customHeight="true">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -27131,7 +27602,7 @@
       <c r="AG728" s="1"/>
       <c r="AH728" s="1"/>
     </row>
-    <row r="729" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="729" ht="12.75" customHeight="true">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -27167,7 +27638,7 @@
       <c r="AG729" s="1"/>
       <c r="AH729" s="1"/>
     </row>
-    <row r="730" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="730" ht="12.75" customHeight="true">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -27203,7 +27674,7 @@
       <c r="AG730" s="1"/>
       <c r="AH730" s="1"/>
     </row>
-    <row r="731" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="731" ht="12.75" customHeight="true">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -27239,7 +27710,7 @@
       <c r="AG731" s="1"/>
       <c r="AH731" s="1"/>
     </row>
-    <row r="732" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="732" ht="12.75" customHeight="true">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -27275,7 +27746,7 @@
       <c r="AG732" s="1"/>
       <c r="AH732" s="1"/>
     </row>
-    <row r="733" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="733" ht="12.75" customHeight="true">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -27311,7 +27782,7 @@
       <c r="AG733" s="1"/>
       <c r="AH733" s="1"/>
     </row>
-    <row r="734" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="734" ht="12.75" customHeight="true">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -27347,7 +27818,7 @@
       <c r="AG734" s="1"/>
       <c r="AH734" s="1"/>
     </row>
-    <row r="735" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="735" ht="12.75" customHeight="true">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -27383,7 +27854,7 @@
       <c r="AG735" s="1"/>
       <c r="AH735" s="1"/>
     </row>
-    <row r="736" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="736" ht="12.75" customHeight="true">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -27419,7 +27890,7 @@
       <c r="AG736" s="1"/>
       <c r="AH736" s="1"/>
     </row>
-    <row r="737" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="737" ht="12.75" customHeight="true">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -27455,7 +27926,7 @@
       <c r="AG737" s="1"/>
       <c r="AH737" s="1"/>
     </row>
-    <row r="738" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="738" ht="12.75" customHeight="true">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -27491,7 +27962,7 @@
       <c r="AG738" s="1"/>
       <c r="AH738" s="1"/>
     </row>
-    <row r="739" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="739" ht="12.75" customHeight="true">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -27527,7 +27998,7 @@
       <c r="AG739" s="1"/>
       <c r="AH739" s="1"/>
     </row>
-    <row r="740" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="740" ht="12.75" customHeight="true">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -27563,7 +28034,7 @@
       <c r="AG740" s="1"/>
       <c r="AH740" s="1"/>
     </row>
-    <row r="741" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="741" ht="12.75" customHeight="true">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -27599,7 +28070,7 @@
       <c r="AG741" s="1"/>
       <c r="AH741" s="1"/>
     </row>
-    <row r="742" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="742" ht="12.75" customHeight="true">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -27635,7 +28106,7 @@
       <c r="AG742" s="1"/>
       <c r="AH742" s="1"/>
     </row>
-    <row r="743" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="743" ht="12.75" customHeight="true">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -27671,7 +28142,7 @@
       <c r="AG743" s="1"/>
       <c r="AH743" s="1"/>
     </row>
-    <row r="744" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="744" ht="12.75" customHeight="true">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -27707,7 +28178,7 @@
       <c r="AG744" s="1"/>
       <c r="AH744" s="1"/>
     </row>
-    <row r="745" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="745" ht="12.75" customHeight="true">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -27743,7 +28214,7 @@
       <c r="AG745" s="1"/>
       <c r="AH745" s="1"/>
     </row>
-    <row r="746" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="746" ht="12.75" customHeight="true">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -27779,7 +28250,7 @@
       <c r="AG746" s="1"/>
       <c r="AH746" s="1"/>
     </row>
-    <row r="747" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="747" ht="12.75" customHeight="true">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -27815,7 +28286,7 @@
       <c r="AG747" s="1"/>
       <c r="AH747" s="1"/>
     </row>
-    <row r="748" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="748" ht="12.75" customHeight="true">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -27851,7 +28322,7 @@
       <c r="AG748" s="1"/>
       <c r="AH748" s="1"/>
     </row>
-    <row r="749" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="749" ht="12.75" customHeight="true">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -27887,7 +28358,7 @@
       <c r="AG749" s="1"/>
       <c r="AH749" s="1"/>
     </row>
-    <row r="750" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="750" ht="12.75" customHeight="true">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -27923,7 +28394,7 @@
       <c r="AG750" s="1"/>
       <c r="AH750" s="1"/>
     </row>
-    <row r="751" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="751" ht="12.75" customHeight="true">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -27959,7 +28430,7 @@
       <c r="AG751" s="1"/>
       <c r="AH751" s="1"/>
     </row>
-    <row r="752" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="752" ht="12.75" customHeight="true">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -27995,7 +28466,7 @@
       <c r="AG752" s="1"/>
       <c r="AH752" s="1"/>
     </row>
-    <row r="753" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="753" ht="12.75" customHeight="true">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -28031,7 +28502,7 @@
       <c r="AG753" s="1"/>
       <c r="AH753" s="1"/>
     </row>
-    <row r="754" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="754" ht="12.75" customHeight="true">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -28067,7 +28538,7 @@
       <c r="AG754" s="1"/>
       <c r="AH754" s="1"/>
     </row>
-    <row r="755" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="755" ht="12.75" customHeight="true">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -28103,7 +28574,7 @@
       <c r="AG755" s="1"/>
       <c r="AH755" s="1"/>
     </row>
-    <row r="756" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="756" ht="12.75" customHeight="true">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -28139,7 +28610,7 @@
       <c r="AG756" s="1"/>
       <c r="AH756" s="1"/>
     </row>
-    <row r="757" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="757" ht="12.75" customHeight="true">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -28175,7 +28646,7 @@
       <c r="AG757" s="1"/>
       <c r="AH757" s="1"/>
     </row>
-    <row r="758" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="758" ht="12.75" customHeight="true">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -28211,7 +28682,7 @@
       <c r="AG758" s="1"/>
       <c r="AH758" s="1"/>
     </row>
-    <row r="759" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="759" ht="12.75" customHeight="true">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -28247,7 +28718,7 @@
       <c r="AG759" s="1"/>
       <c r="AH759" s="1"/>
     </row>
-    <row r="760" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="760" ht="12.75" customHeight="true">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -28283,7 +28754,7 @@
       <c r="AG760" s="1"/>
       <c r="AH760" s="1"/>
     </row>
-    <row r="761" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="761" ht="12.75" customHeight="true">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -28319,7 +28790,7 @@
       <c r="AG761" s="1"/>
       <c r="AH761" s="1"/>
     </row>
-    <row r="762" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="762" ht="12.75" customHeight="true">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -28355,7 +28826,7 @@
       <c r="AG762" s="1"/>
       <c r="AH762" s="1"/>
     </row>
-    <row r="763" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="763" ht="12.75" customHeight="true">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -28391,7 +28862,7 @@
       <c r="AG763" s="1"/>
       <c r="AH763" s="1"/>
     </row>
-    <row r="764" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="764" ht="12.75" customHeight="true">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -28427,7 +28898,7 @@
       <c r="AG764" s="1"/>
       <c r="AH764" s="1"/>
     </row>
-    <row r="765" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="765" ht="12.75" customHeight="true">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -28463,7 +28934,7 @@
       <c r="AG765" s="1"/>
       <c r="AH765" s="1"/>
     </row>
-    <row r="766" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="766" ht="12.75" customHeight="true">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -28499,7 +28970,7 @@
       <c r="AG766" s="1"/>
       <c r="AH766" s="1"/>
     </row>
-    <row r="767" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="767" ht="12.75" customHeight="true">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -28535,7 +29006,7 @@
       <c r="AG767" s="1"/>
       <c r="AH767" s="1"/>
     </row>
-    <row r="768" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="768" ht="12.75" customHeight="true">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -28571,7 +29042,7 @@
       <c r="AG768" s="1"/>
       <c r="AH768" s="1"/>
     </row>
-    <row r="769" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="769" ht="12.75" customHeight="true">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -28607,7 +29078,7 @@
       <c r="AG769" s="1"/>
       <c r="AH769" s="1"/>
     </row>
-    <row r="770" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="770" ht="12.75" customHeight="true">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -28643,7 +29114,7 @@
       <c r="AG770" s="1"/>
       <c r="AH770" s="1"/>
     </row>
-    <row r="771" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="771" ht="12.75" customHeight="true">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -28679,7 +29150,7 @@
       <c r="AG771" s="1"/>
       <c r="AH771" s="1"/>
     </row>
-    <row r="772" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="772" ht="12.75" customHeight="true">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -28715,7 +29186,7 @@
       <c r="AG772" s="1"/>
       <c r="AH772" s="1"/>
     </row>
-    <row r="773" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="773" ht="12.75" customHeight="true">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -28751,7 +29222,7 @@
       <c r="AG773" s="1"/>
       <c r="AH773" s="1"/>
     </row>
-    <row r="774" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="774" ht="12.75" customHeight="true">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -28787,7 +29258,7 @@
       <c r="AG774" s="1"/>
       <c r="AH774" s="1"/>
     </row>
-    <row r="775" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="775" ht="12.75" customHeight="true">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -28823,7 +29294,7 @@
       <c r="AG775" s="1"/>
       <c r="AH775" s="1"/>
     </row>
-    <row r="776" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="776" ht="12.75" customHeight="true">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -28859,7 +29330,7 @@
       <c r="AG776" s="1"/>
       <c r="AH776" s="1"/>
     </row>
-    <row r="777" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="777" ht="12.75" customHeight="true">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -28895,7 +29366,7 @@
       <c r="AG777" s="1"/>
       <c r="AH777" s="1"/>
     </row>
-    <row r="778" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="778" ht="12.75" customHeight="true">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -28931,7 +29402,7 @@
       <c r="AG778" s="1"/>
       <c r="AH778" s="1"/>
     </row>
-    <row r="779" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="779" ht="12.75" customHeight="true">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -28967,7 +29438,7 @@
       <c r="AG779" s="1"/>
       <c r="AH779" s="1"/>
     </row>
-    <row r="780" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="780" ht="12.75" customHeight="true">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -29003,7 +29474,7 @@
       <c r="AG780" s="1"/>
       <c r="AH780" s="1"/>
     </row>
-    <row r="781" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="781" ht="12.75" customHeight="true">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -29039,7 +29510,7 @@
       <c r="AG781" s="1"/>
       <c r="AH781" s="1"/>
     </row>
-    <row r="782" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="782" ht="12.75" customHeight="true">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -29075,7 +29546,7 @@
       <c r="AG782" s="1"/>
       <c r="AH782" s="1"/>
     </row>
-    <row r="783" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="783" ht="12.75" customHeight="true">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -29111,7 +29582,7 @@
       <c r="AG783" s="1"/>
       <c r="AH783" s="1"/>
     </row>
-    <row r="784" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="784" ht="12.75" customHeight="true">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -29147,7 +29618,7 @@
       <c r="AG784" s="1"/>
       <c r="AH784" s="1"/>
     </row>
-    <row r="785" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="785" ht="12.75" customHeight="true">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -29183,7 +29654,7 @@
       <c r="AG785" s="1"/>
       <c r="AH785" s="1"/>
     </row>
-    <row r="786" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="786" ht="12.75" customHeight="true">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -29219,7 +29690,7 @@
       <c r="AG786" s="1"/>
       <c r="AH786" s="1"/>
     </row>
-    <row r="787" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="787" ht="12.75" customHeight="true">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -29255,7 +29726,7 @@
       <c r="AG787" s="1"/>
       <c r="AH787" s="1"/>
     </row>
-    <row r="788" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="788" ht="12.75" customHeight="true">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -29291,7 +29762,7 @@
       <c r="AG788" s="1"/>
       <c r="AH788" s="1"/>
     </row>
-    <row r="789" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="789" ht="12.75" customHeight="true">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -29327,7 +29798,7 @@
       <c r="AG789" s="1"/>
       <c r="AH789" s="1"/>
     </row>
-    <row r="790" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="790" ht="12.75" customHeight="true">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -29363,7 +29834,7 @@
       <c r="AG790" s="1"/>
       <c r="AH790" s="1"/>
     </row>
-    <row r="791" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="791" ht="12.75" customHeight="true">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -29399,7 +29870,7 @@
       <c r="AG791" s="1"/>
       <c r="AH791" s="1"/>
     </row>
-    <row r="792" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="792" ht="12.75" customHeight="true">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -29435,7 +29906,7 @@
       <c r="AG792" s="1"/>
       <c r="AH792" s="1"/>
     </row>
-    <row r="793" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="793" ht="12.75" customHeight="true">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -29471,7 +29942,7 @@
       <c r="AG793" s="1"/>
       <c r="AH793" s="1"/>
     </row>
-    <row r="794" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="794" ht="12.75" customHeight="true">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -29507,7 +29978,7 @@
       <c r="AG794" s="1"/>
       <c r="AH794" s="1"/>
     </row>
-    <row r="795" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="795" ht="12.75" customHeight="true">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -29543,7 +30014,7 @@
       <c r="AG795" s="1"/>
       <c r="AH795" s="1"/>
     </row>
-    <row r="796" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="796" ht="12.75" customHeight="true">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -29579,7 +30050,7 @@
       <c r="AG796" s="1"/>
       <c r="AH796" s="1"/>
     </row>
-    <row r="797" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="797" ht="12.75" customHeight="true">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -29615,7 +30086,7 @@
       <c r="AG797" s="1"/>
       <c r="AH797" s="1"/>
     </row>
-    <row r="798" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="798" ht="12.75" customHeight="true">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -29651,7 +30122,7 @@
       <c r="AG798" s="1"/>
       <c r="AH798" s="1"/>
     </row>
-    <row r="799" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="799" ht="12.75" customHeight="true">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -29687,7 +30158,7 @@
       <c r="AG799" s="1"/>
       <c r="AH799" s="1"/>
     </row>
-    <row r="800" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="800" ht="12.75" customHeight="true">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -29723,7 +30194,7 @@
       <c r="AG800" s="1"/>
       <c r="AH800" s="1"/>
     </row>
-    <row r="801" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="801" ht="12.75" customHeight="true">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -29759,7 +30230,7 @@
       <c r="AG801" s="1"/>
       <c r="AH801" s="1"/>
     </row>
-    <row r="802" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="802" ht="12.75" customHeight="true">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -29795,7 +30266,7 @@
       <c r="AG802" s="1"/>
       <c r="AH802" s="1"/>
     </row>
-    <row r="803" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="803" ht="12.75" customHeight="true">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -29831,7 +30302,7 @@
       <c r="AG803" s="1"/>
       <c r="AH803" s="1"/>
     </row>
-    <row r="804" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="804" ht="12.75" customHeight="true">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -29867,7 +30338,7 @@
       <c r="AG804" s="1"/>
       <c r="AH804" s="1"/>
     </row>
-    <row r="805" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="805" ht="12.75" customHeight="true">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -29903,7 +30374,7 @@
       <c r="AG805" s="1"/>
       <c r="AH805" s="1"/>
     </row>
-    <row r="806" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="806" ht="12.75" customHeight="true">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -29939,7 +30410,7 @@
       <c r="AG806" s="1"/>
       <c r="AH806" s="1"/>
     </row>
-    <row r="807" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="807" ht="12.75" customHeight="true">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -29975,7 +30446,7 @@
       <c r="AG807" s="1"/>
       <c r="AH807" s="1"/>
     </row>
-    <row r="808" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="808" ht="12.75" customHeight="true">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -30011,7 +30482,7 @@
       <c r="AG808" s="1"/>
       <c r="AH808" s="1"/>
     </row>
-    <row r="809" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="809" ht="12.75" customHeight="true">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -30047,7 +30518,7 @@
       <c r="AG809" s="1"/>
       <c r="AH809" s="1"/>
     </row>
-    <row r="810" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="810" ht="12.75" customHeight="true">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -30083,7 +30554,7 @@
       <c r="AG810" s="1"/>
       <c r="AH810" s="1"/>
     </row>
-    <row r="811" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="811" ht="12.75" customHeight="true">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -30119,7 +30590,7 @@
       <c r="AG811" s="1"/>
       <c r="AH811" s="1"/>
     </row>
-    <row r="812" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="812" ht="12.75" customHeight="true">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -30155,7 +30626,7 @@
       <c r="AG812" s="1"/>
       <c r="AH812" s="1"/>
     </row>
-    <row r="813" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="813" ht="12.75" customHeight="true">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -30191,7 +30662,7 @@
       <c r="AG813" s="1"/>
       <c r="AH813" s="1"/>
     </row>
-    <row r="814" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="814" ht="12.75" customHeight="true">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -30227,7 +30698,7 @@
       <c r="AG814" s="1"/>
       <c r="AH814" s="1"/>
     </row>
-    <row r="815" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="815" ht="12.75" customHeight="true">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -30263,7 +30734,7 @@
       <c r="AG815" s="1"/>
       <c r="AH815" s="1"/>
     </row>
-    <row r="816" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="816" ht="12.75" customHeight="true">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -30299,7 +30770,7 @@
       <c r="AG816" s="1"/>
       <c r="AH816" s="1"/>
     </row>
-    <row r="817" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="817" ht="12.75" customHeight="true">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -30335,7 +30806,7 @@
       <c r="AG817" s="1"/>
       <c r="AH817" s="1"/>
     </row>
-    <row r="818" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="818" ht="12.75" customHeight="true">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -30371,7 +30842,7 @@
       <c r="AG818" s="1"/>
       <c r="AH818" s="1"/>
     </row>
-    <row r="819" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="819" ht="12.75" customHeight="true">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -30407,7 +30878,7 @@
       <c r="AG819" s="1"/>
       <c r="AH819" s="1"/>
     </row>
-    <row r="820" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="820" ht="12.75" customHeight="true">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -30443,7 +30914,7 @@
       <c r="AG820" s="1"/>
       <c r="AH820" s="1"/>
     </row>
-    <row r="821" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="821" ht="12.75" customHeight="true">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -30479,7 +30950,7 @@
       <c r="AG821" s="1"/>
       <c r="AH821" s="1"/>
     </row>
-    <row r="822" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="822" ht="12.75" customHeight="true">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -30515,7 +30986,7 @@
       <c r="AG822" s="1"/>
       <c r="AH822" s="1"/>
     </row>
-    <row r="823" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="823" ht="12.75" customHeight="true">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -30551,7 +31022,7 @@
       <c r="AG823" s="1"/>
       <c r="AH823" s="1"/>
     </row>
-    <row r="824" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="824" ht="12.75" customHeight="true">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -30587,7 +31058,7 @@
       <c r="AG824" s="1"/>
       <c r="AH824" s="1"/>
     </row>
-    <row r="825" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="825" ht="12.75" customHeight="true">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -30623,7 +31094,7 @@
       <c r="AG825" s="1"/>
       <c r="AH825" s="1"/>
     </row>
-    <row r="826" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="826" ht="12.75" customHeight="true">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -30659,7 +31130,7 @@
       <c r="AG826" s="1"/>
       <c r="AH826" s="1"/>
     </row>
-    <row r="827" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="827" ht="12.75" customHeight="true">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -30695,7 +31166,7 @@
       <c r="AG827" s="1"/>
       <c r="AH827" s="1"/>
     </row>
-    <row r="828" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="828" ht="12.75" customHeight="true">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -30731,7 +31202,7 @@
       <c r="AG828" s="1"/>
       <c r="AH828" s="1"/>
     </row>
-    <row r="829" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="829" ht="12.75" customHeight="true">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -30767,7 +31238,7 @@
       <c r="AG829" s="1"/>
       <c r="AH829" s="1"/>
     </row>
-    <row r="830" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="830" ht="12.75" customHeight="true">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -30803,7 +31274,7 @@
       <c r="AG830" s="1"/>
       <c r="AH830" s="1"/>
     </row>
-    <row r="831" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="831" ht="12.75" customHeight="true">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -30839,7 +31310,7 @@
       <c r="AG831" s="1"/>
       <c r="AH831" s="1"/>
     </row>
-    <row r="832" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="832" ht="12.75" customHeight="true">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -30875,7 +31346,7 @@
       <c r="AG832" s="1"/>
       <c r="AH832" s="1"/>
     </row>
-    <row r="833" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="833" ht="12.75" customHeight="true">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -30911,7 +31382,7 @@
       <c r="AG833" s="1"/>
       <c r="AH833" s="1"/>
     </row>
-    <row r="834" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="834" ht="12.75" customHeight="true">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -30947,7 +31418,7 @@
       <c r="AG834" s="1"/>
       <c r="AH834" s="1"/>
     </row>
-    <row r="835" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="835" ht="12.75" customHeight="true">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -30983,7 +31454,7 @@
       <c r="AG835" s="1"/>
       <c r="AH835" s="1"/>
     </row>
-    <row r="836" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="836" ht="12.75" customHeight="true">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -31019,7 +31490,7 @@
       <c r="AG836" s="1"/>
       <c r="AH836" s="1"/>
     </row>
-    <row r="837" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="837" ht="12.75" customHeight="true">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -31055,7 +31526,7 @@
       <c r="AG837" s="1"/>
       <c r="AH837" s="1"/>
     </row>
-    <row r="838" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="838" ht="12.75" customHeight="true">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -31091,7 +31562,7 @@
       <c r="AG838" s="1"/>
       <c r="AH838" s="1"/>
     </row>
-    <row r="839" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="839" ht="12.75" customHeight="true">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -31127,7 +31598,7 @@
       <c r="AG839" s="1"/>
       <c r="AH839" s="1"/>
     </row>
-    <row r="840" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="840" ht="12.75" customHeight="true">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -31163,7 +31634,7 @@
       <c r="AG840" s="1"/>
       <c r="AH840" s="1"/>
     </row>
-    <row r="841" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="841" ht="12.75" customHeight="true">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -31199,7 +31670,7 @@
       <c r="AG841" s="1"/>
       <c r="AH841" s="1"/>
     </row>
-    <row r="842" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="842" ht="12.75" customHeight="true">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -31235,7 +31706,7 @@
       <c r="AG842" s="1"/>
       <c r="AH842" s="1"/>
     </row>
-    <row r="843" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="843" ht="12.75" customHeight="true">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -31271,7 +31742,7 @@
       <c r="AG843" s="1"/>
       <c r="AH843" s="1"/>
     </row>
-    <row r="844" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="844" ht="12.75" customHeight="true">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -31307,7 +31778,7 @@
       <c r="AG844" s="1"/>
       <c r="AH844" s="1"/>
     </row>
-    <row r="845" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="845" ht="12.75" customHeight="true">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -31343,7 +31814,7 @@
       <c r="AG845" s="1"/>
       <c r="AH845" s="1"/>
     </row>
-    <row r="846" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="846" ht="12.75" customHeight="true">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -31379,7 +31850,7 @@
       <c r="AG846" s="1"/>
       <c r="AH846" s="1"/>
     </row>
-    <row r="847" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="847" ht="12.75" customHeight="true">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -31415,7 +31886,7 @@
       <c r="AG847" s="1"/>
       <c r="AH847" s="1"/>
     </row>
-    <row r="848" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="848" ht="12.75" customHeight="true">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -31451,7 +31922,7 @@
       <c r="AG848" s="1"/>
       <c r="AH848" s="1"/>
     </row>
-    <row r="849" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="849" ht="12.75" customHeight="true">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -31487,7 +31958,7 @@
       <c r="AG849" s="1"/>
       <c r="AH849" s="1"/>
     </row>
-    <row r="850" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="850" ht="12.75" customHeight="true">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -31523,7 +31994,7 @@
       <c r="AG850" s="1"/>
       <c r="AH850" s="1"/>
     </row>
-    <row r="851" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="851" ht="12.75" customHeight="true">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -31559,7 +32030,7 @@
       <c r="AG851" s="1"/>
       <c r="AH851" s="1"/>
     </row>
-    <row r="852" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="852" ht="12.75" customHeight="true">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -31595,7 +32066,7 @@
       <c r="AG852" s="1"/>
       <c r="AH852" s="1"/>
     </row>
-    <row r="853" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="853" ht="12.75" customHeight="true">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -31631,7 +32102,7 @@
       <c r="AG853" s="1"/>
       <c r="AH853" s="1"/>
     </row>
-    <row r="854" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="854" ht="12.75" customHeight="true">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -31667,7 +32138,7 @@
       <c r="AG854" s="1"/>
       <c r="AH854" s="1"/>
     </row>
-    <row r="855" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="855" ht="12.75" customHeight="true">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -31703,7 +32174,7 @@
       <c r="AG855" s="1"/>
       <c r="AH855" s="1"/>
     </row>
-    <row r="856" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="856" ht="12.75" customHeight="true">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -31739,7 +32210,7 @@
       <c r="AG856" s="1"/>
       <c r="AH856" s="1"/>
     </row>
-    <row r="857" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="857" ht="12.75" customHeight="true">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -31775,7 +32246,7 @@
       <c r="AG857" s="1"/>
       <c r="AH857" s="1"/>
     </row>
-    <row r="858" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="858" ht="12.75" customHeight="true">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -31811,7 +32282,7 @@
       <c r="AG858" s="1"/>
       <c r="AH858" s="1"/>
     </row>
-    <row r="859" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="859" ht="12.75" customHeight="true">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -31847,7 +32318,7 @@
       <c r="AG859" s="1"/>
       <c r="AH859" s="1"/>
     </row>
-    <row r="860" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="860" ht="12.75" customHeight="true">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -31883,7 +32354,7 @@
       <c r="AG860" s="1"/>
       <c r="AH860" s="1"/>
     </row>
-    <row r="861" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="861" ht="12.75" customHeight="true">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -31919,7 +32390,7 @@
       <c r="AG861" s="1"/>
       <c r="AH861" s="1"/>
     </row>
-    <row r="862" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="862" ht="12.75" customHeight="true">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -31955,7 +32426,7 @@
       <c r="AG862" s="1"/>
       <c r="AH862" s="1"/>
     </row>
-    <row r="863" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="863" ht="12.75" customHeight="true">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -31991,7 +32462,7 @@
       <c r="AG863" s="1"/>
       <c r="AH863" s="1"/>
     </row>
-    <row r="864" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="864" ht="12.75" customHeight="true">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -32027,7 +32498,7 @@
       <c r="AG864" s="1"/>
       <c r="AH864" s="1"/>
     </row>
-    <row r="865" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="865" ht="12.75" customHeight="true">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -32063,7 +32534,7 @@
       <c r="AG865" s="1"/>
       <c r="AH865" s="1"/>
     </row>
-    <row r="866" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="866" ht="12.75" customHeight="true">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -32099,7 +32570,7 @@
       <c r="AG866" s="1"/>
       <c r="AH866" s="1"/>
     </row>
-    <row r="867" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="867" ht="12.75" customHeight="true">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -32135,7 +32606,7 @@
       <c r="AG867" s="1"/>
       <c r="AH867" s="1"/>
     </row>
-    <row r="868" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="868" ht="12.75" customHeight="true">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -32171,7 +32642,7 @@
       <c r="AG868" s="1"/>
       <c r="AH868" s="1"/>
     </row>
-    <row r="869" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="869" ht="12.75" customHeight="true">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -32207,7 +32678,7 @@
       <c r="AG869" s="1"/>
       <c r="AH869" s="1"/>
     </row>
-    <row r="870" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="870" ht="12.75" customHeight="true">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -32243,7 +32714,7 @@
       <c r="AG870" s="1"/>
       <c r="AH870" s="1"/>
     </row>
-    <row r="871" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="871" ht="12.75" customHeight="true">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -32279,7 +32750,7 @@
       <c r="AG871" s="1"/>
       <c r="AH871" s="1"/>
     </row>
-    <row r="872" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="872" ht="12.75" customHeight="true">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -32315,7 +32786,7 @@
       <c r="AG872" s="1"/>
       <c r="AH872" s="1"/>
     </row>
-    <row r="873" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="873" ht="12.75" customHeight="true">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -32351,7 +32822,7 @@
       <c r="AG873" s="1"/>
       <c r="AH873" s="1"/>
     </row>
-    <row r="874" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="874" ht="12.75" customHeight="true">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -32387,7 +32858,7 @@
       <c r="AG874" s="1"/>
       <c r="AH874" s="1"/>
     </row>
-    <row r="875" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="875" ht="12.75" customHeight="true">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -32423,7 +32894,7 @@
       <c r="AG875" s="1"/>
       <c r="AH875" s="1"/>
     </row>
-    <row r="876" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="876" ht="12.75" customHeight="true">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -32459,7 +32930,7 @@
       <c r="AG876" s="1"/>
       <c r="AH876" s="1"/>
     </row>
-    <row r="877" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="877" ht="12.75" customHeight="true">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -32495,7 +32966,7 @@
       <c r="AG877" s="1"/>
       <c r="AH877" s="1"/>
     </row>
-    <row r="878" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="878" ht="12.75" customHeight="true">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -32531,7 +33002,7 @@
       <c r="AG878" s="1"/>
       <c r="AH878" s="1"/>
     </row>
-    <row r="879" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="879" ht="12.75" customHeight="true">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -32567,7 +33038,7 @@
       <c r="AG879" s="1"/>
       <c r="AH879" s="1"/>
     </row>
-    <row r="880" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="880" ht="12.75" customHeight="true">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -32603,7 +33074,7 @@
       <c r="AG880" s="1"/>
       <c r="AH880" s="1"/>
     </row>
-    <row r="881" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="881" ht="12.75" customHeight="true">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -32639,7 +33110,7 @@
       <c r="AG881" s="1"/>
       <c r="AH881" s="1"/>
     </row>
-    <row r="882" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="882" ht="12.75" customHeight="true">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -32675,7 +33146,7 @@
       <c r="AG882" s="1"/>
       <c r="AH882" s="1"/>
     </row>
-    <row r="883" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="883" ht="12.75" customHeight="true">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -32711,7 +33182,7 @@
       <c r="AG883" s="1"/>
       <c r="AH883" s="1"/>
     </row>
-    <row r="884" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="884" ht="12.75" customHeight="true">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -32747,7 +33218,7 @@
       <c r="AG884" s="1"/>
       <c r="AH884" s="1"/>
     </row>
-    <row r="885" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="885" ht="12.75" customHeight="true">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -32783,7 +33254,7 @@
       <c r="AG885" s="1"/>
       <c r="AH885" s="1"/>
     </row>
-    <row r="886" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="886" ht="12.75" customHeight="true">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -32819,7 +33290,7 @@
       <c r="AG886" s="1"/>
       <c r="AH886" s="1"/>
     </row>
-    <row r="887" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="887" ht="12.75" customHeight="true">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -32855,7 +33326,7 @@
       <c r="AG887" s="1"/>
       <c r="AH887" s="1"/>
     </row>
-    <row r="888" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="888" ht="12.75" customHeight="true">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -32891,7 +33362,7 @@
       <c r="AG888" s="1"/>
       <c r="AH888" s="1"/>
     </row>
-    <row r="889" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="889" ht="12.75" customHeight="true">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -32927,7 +33398,7 @@
       <c r="AG889" s="1"/>
       <c r="AH889" s="1"/>
     </row>
-    <row r="890" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="890" ht="12.75" customHeight="true">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -32963,7 +33434,7 @@
       <c r="AG890" s="1"/>
       <c r="AH890" s="1"/>
     </row>
-    <row r="891" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="891" ht="12.75" customHeight="true">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -32999,7 +33470,7 @@
       <c r="AG891" s="1"/>
       <c r="AH891" s="1"/>
     </row>
-    <row r="892" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="892" ht="12.75" customHeight="true">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -33035,7 +33506,7 @@
       <c r="AG892" s="1"/>
       <c r="AH892" s="1"/>
     </row>
-    <row r="893" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="893" ht="12.75" customHeight="true">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -33071,7 +33542,7 @@
       <c r="AG893" s="1"/>
       <c r="AH893" s="1"/>
     </row>
-    <row r="894" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="894" ht="12.75" customHeight="true">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -33107,7 +33578,7 @@
       <c r="AG894" s="1"/>
       <c r="AH894" s="1"/>
     </row>
-    <row r="895" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="895" ht="12.75" customHeight="true">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -33143,7 +33614,7 @@
       <c r="AG895" s="1"/>
       <c r="AH895" s="1"/>
     </row>
-    <row r="896" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="896" ht="12.75" customHeight="true">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -33179,7 +33650,7 @@
       <c r="AG896" s="1"/>
       <c r="AH896" s="1"/>
     </row>
-    <row r="897" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="897" ht="12.75" customHeight="true">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -33215,7 +33686,7 @@
       <c r="AG897" s="1"/>
       <c r="AH897" s="1"/>
     </row>
-    <row r="898" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="898" ht="12.75" customHeight="true">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -33251,7 +33722,7 @@
       <c r="AG898" s="1"/>
       <c r="AH898" s="1"/>
     </row>
-    <row r="899" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="899" ht="12.75" customHeight="true">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -33287,7 +33758,7 @@
       <c r="AG899" s="1"/>
       <c r="AH899" s="1"/>
     </row>
-    <row r="900" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="900" ht="12.75" customHeight="true">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -33323,7 +33794,7 @@
       <c r="AG900" s="1"/>
       <c r="AH900" s="1"/>
     </row>
-    <row r="901" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="901" ht="12.75" customHeight="true">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -33359,7 +33830,7 @@
       <c r="AG901" s="1"/>
       <c r="AH901" s="1"/>
     </row>
-    <row r="902" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="902" ht="12.75" customHeight="true">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -33395,7 +33866,7 @@
       <c r="AG902" s="1"/>
       <c r="AH902" s="1"/>
     </row>
-    <row r="903" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="903" ht="12.75" customHeight="true">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -33431,7 +33902,7 @@
       <c r="AG903" s="1"/>
       <c r="AH903" s="1"/>
     </row>
-    <row r="904" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="904" ht="12.75" customHeight="true">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -33467,7 +33938,7 @@
       <c r="AG904" s="1"/>
       <c r="AH904" s="1"/>
     </row>
-    <row r="905" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="905" ht="12.75" customHeight="true">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -33503,7 +33974,7 @@
       <c r="AG905" s="1"/>
       <c r="AH905" s="1"/>
     </row>
-    <row r="906" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="906" ht="12.75" customHeight="true">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -33539,7 +34010,7 @@
       <c r="AG906" s="1"/>
       <c r="AH906" s="1"/>
     </row>
-    <row r="907" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="907" ht="12.75" customHeight="true">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -33575,7 +34046,7 @@
       <c r="AG907" s="1"/>
       <c r="AH907" s="1"/>
     </row>
-    <row r="908" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="908" ht="12.75" customHeight="true">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -33611,7 +34082,7 @@
       <c r="AG908" s="1"/>
       <c r="AH908" s="1"/>
     </row>
-    <row r="909" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="909" ht="12.75" customHeight="true">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -33647,7 +34118,7 @@
       <c r="AG909" s="1"/>
       <c r="AH909" s="1"/>
     </row>
-    <row r="910" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="910" ht="12.75" customHeight="true">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -33683,7 +34154,7 @@
       <c r="AG910" s="1"/>
       <c r="AH910" s="1"/>
     </row>
-    <row r="911" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="911" ht="12.75" customHeight="true">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -33719,7 +34190,7 @@
       <c r="AG911" s="1"/>
       <c r="AH911" s="1"/>
     </row>
-    <row r="912" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="912" ht="12.75" customHeight="true">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -33755,7 +34226,7 @@
       <c r="AG912" s="1"/>
       <c r="AH912" s="1"/>
     </row>
-    <row r="913" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="913" ht="12.75" customHeight="true">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -33791,7 +34262,7 @@
       <c r="AG913" s="1"/>
       <c r="AH913" s="1"/>
     </row>
-    <row r="914" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="914" ht="12.75" customHeight="true">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -33827,7 +34298,7 @@
       <c r="AG914" s="1"/>
       <c r="AH914" s="1"/>
     </row>
-    <row r="915" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="915" ht="12.75" customHeight="true">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -33863,7 +34334,7 @@
       <c r="AG915" s="1"/>
       <c r="AH915" s="1"/>
     </row>
-    <row r="916" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="916" ht="12.75" customHeight="true">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -33899,7 +34370,7 @@
       <c r="AG916" s="1"/>
       <c r="AH916" s="1"/>
     </row>
-    <row r="917" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="917" ht="12.75" customHeight="true">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -33935,7 +34406,7 @@
       <c r="AG917" s="1"/>
       <c r="AH917" s="1"/>
     </row>
-    <row r="918" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="918" ht="12.75" customHeight="true">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -33971,7 +34442,7 @@
       <c r="AG918" s="1"/>
       <c r="AH918" s="1"/>
     </row>
-    <row r="919" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="919" ht="12.75" customHeight="true">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -34007,7 +34478,7 @@
       <c r="AG919" s="1"/>
       <c r="AH919" s="1"/>
     </row>
-    <row r="920" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="920" ht="12.75" customHeight="true">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -34043,7 +34514,7 @@
       <c r="AG920" s="1"/>
       <c r="AH920" s="1"/>
     </row>
-    <row r="921" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="921" ht="12.75" customHeight="true">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -34079,7 +34550,7 @@
       <c r="AG921" s="1"/>
       <c r="AH921" s="1"/>
     </row>
-    <row r="922" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="922" ht="12.75" customHeight="true">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -34115,7 +34586,7 @@
       <c r="AG922" s="1"/>
       <c r="AH922" s="1"/>
     </row>
-    <row r="923" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="923" ht="12.75" customHeight="true">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -34151,7 +34622,7 @@
       <c r="AG923" s="1"/>
       <c r="AH923" s="1"/>
     </row>
-    <row r="924" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="924" ht="12.75" customHeight="true">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -34187,7 +34658,7 @@
       <c r="AG924" s="1"/>
       <c r="AH924" s="1"/>
     </row>
-    <row r="925" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="925" ht="12.75" customHeight="true">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -34223,7 +34694,7 @@
       <c r="AG925" s="1"/>
       <c r="AH925" s="1"/>
     </row>
-    <row r="926" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="926" ht="12.75" customHeight="true">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -34259,7 +34730,7 @@
       <c r="AG926" s="1"/>
       <c r="AH926" s="1"/>
     </row>
-    <row r="927" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="927" ht="12.75" customHeight="true">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -34295,7 +34766,7 @@
       <c r="AG927" s="1"/>
       <c r="AH927" s="1"/>
     </row>
-    <row r="928" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="928" ht="12.75" customHeight="true">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -34331,7 +34802,7 @@
       <c r="AG928" s="1"/>
       <c r="AH928" s="1"/>
     </row>
-    <row r="929" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="929" ht="12.75" customHeight="true">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -34367,7 +34838,7 @@
       <c r="AG929" s="1"/>
       <c r="AH929" s="1"/>
     </row>
-    <row r="930" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="930" ht="12.75" customHeight="true">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -34403,7 +34874,7 @@
       <c r="AG930" s="1"/>
       <c r="AH930" s="1"/>
     </row>
-    <row r="931" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="931" ht="12.75" customHeight="true">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -34439,7 +34910,7 @@
       <c r="AG931" s="1"/>
       <c r="AH931" s="1"/>
     </row>
-    <row r="932" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="932" ht="12.75" customHeight="true">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -34475,7 +34946,7 @@
       <c r="AG932" s="1"/>
       <c r="AH932" s="1"/>
     </row>
-    <row r="933" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="933" ht="12.75" customHeight="true">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -34511,7 +34982,7 @@
       <c r="AG933" s="1"/>
       <c r="AH933" s="1"/>
     </row>
-    <row r="934" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="934" ht="12.75" customHeight="true">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -34547,7 +35018,7 @@
       <c r="AG934" s="1"/>
       <c r="AH934" s="1"/>
     </row>
-    <row r="935" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="935" ht="12.75" customHeight="true">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -34583,7 +35054,7 @@
       <c r="AG935" s="1"/>
       <c r="AH935" s="1"/>
     </row>
-    <row r="936" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="936" ht="12.75" customHeight="true">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -34619,7 +35090,7 @@
       <c r="AG936" s="1"/>
       <c r="AH936" s="1"/>
     </row>
-    <row r="937" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="937" ht="12.75" customHeight="true">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -34655,7 +35126,7 @@
       <c r="AG937" s="1"/>
       <c r="AH937" s="1"/>
     </row>
-    <row r="938" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="938" ht="12.75" customHeight="true">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -34691,7 +35162,7 @@
       <c r="AG938" s="1"/>
       <c r="AH938" s="1"/>
     </row>
-    <row r="939" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="939" ht="12.75" customHeight="true">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -34727,7 +35198,7 @@
       <c r="AG939" s="1"/>
       <c r="AH939" s="1"/>
     </row>
-    <row r="940" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="940" ht="12.75" customHeight="true">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -34763,7 +35234,7 @@
       <c r="AG940" s="1"/>
       <c r="AH940" s="1"/>
     </row>
-    <row r="941" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="941" ht="12.75" customHeight="true">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -34799,7 +35270,7 @@
       <c r="AG941" s="1"/>
       <c r="AH941" s="1"/>
     </row>
-    <row r="942" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="942" ht="12.75" customHeight="true">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -34835,7 +35306,7 @@
       <c r="AG942" s="1"/>
       <c r="AH942" s="1"/>
     </row>
-    <row r="943" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="943" ht="12.75" customHeight="true">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -34871,7 +35342,7 @@
       <c r="AG943" s="1"/>
       <c r="AH943" s="1"/>
     </row>
-    <row r="944" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="944" ht="12.75" customHeight="true">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -34907,7 +35378,7 @@
       <c r="AG944" s="1"/>
       <c r="AH944" s="1"/>
     </row>
-    <row r="945" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="945" ht="12.75" customHeight="true">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -34943,7 +35414,7 @@
       <c r="AG945" s="1"/>
       <c r="AH945" s="1"/>
     </row>
-    <row r="946" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="946" ht="12.75" customHeight="true">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -34979,7 +35450,7 @@
       <c r="AG946" s="1"/>
       <c r="AH946" s="1"/>
     </row>
-    <row r="947" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="947" ht="12.75" customHeight="true">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -35015,7 +35486,7 @@
       <c r="AG947" s="1"/>
       <c r="AH947" s="1"/>
     </row>
-    <row r="948" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="948" ht="12.75" customHeight="true">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -35051,7 +35522,7 @@
       <c r="AG948" s="1"/>
       <c r="AH948" s="1"/>
     </row>
-    <row r="949" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="949" ht="12.75" customHeight="true">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -35087,7 +35558,7 @@
       <c r="AG949" s="1"/>
       <c r="AH949" s="1"/>
     </row>
-    <row r="950" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="950" ht="12.75" customHeight="true">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -35123,7 +35594,7 @@
       <c r="AG950" s="1"/>
       <c r="AH950" s="1"/>
     </row>
-    <row r="951" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="951" ht="12.75" customHeight="true">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -35159,7 +35630,7 @@
       <c r="AG951" s="1"/>
       <c r="AH951" s="1"/>
     </row>
-    <row r="952" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="952" ht="12.75" customHeight="true">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -35195,7 +35666,7 @@
       <c r="AG952" s="1"/>
       <c r="AH952" s="1"/>
     </row>
-    <row r="953" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="953" ht="12.75" customHeight="true">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -35231,7 +35702,7 @@
       <c r="AG953" s="1"/>
       <c r="AH953" s="1"/>
     </row>
-    <row r="954" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="954" ht="12.75" customHeight="true">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -35267,7 +35738,7 @@
       <c r="AG954" s="1"/>
       <c r="AH954" s="1"/>
     </row>
-    <row r="955" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="955" ht="12.75" customHeight="true">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -35303,7 +35774,7 @@
       <c r="AG955" s="1"/>
       <c r="AH955" s="1"/>
     </row>
-    <row r="956" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="956" ht="12.75" customHeight="true">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -35339,7 +35810,7 @@
       <c r="AG956" s="1"/>
       <c r="AH956" s="1"/>
     </row>
-    <row r="957" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="957" ht="12.75" customHeight="true">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -35375,7 +35846,7 @@
       <c r="AG957" s="1"/>
       <c r="AH957" s="1"/>
     </row>
-    <row r="958" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="958" ht="12.75" customHeight="true">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -35411,7 +35882,7 @@
       <c r="AG958" s="1"/>
       <c r="AH958" s="1"/>
     </row>
-    <row r="959" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="959" ht="12.75" customHeight="true">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -35447,7 +35918,7 @@
       <c r="AG959" s="1"/>
       <c r="AH959" s="1"/>
     </row>
-    <row r="960" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="960" ht="12.75" customHeight="true">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -35483,7 +35954,7 @@
       <c r="AG960" s="1"/>
       <c r="AH960" s="1"/>
     </row>
-    <row r="961" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="961" ht="12.75" customHeight="true">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -35519,7 +35990,7 @@
       <c r="AG961" s="1"/>
       <c r="AH961" s="1"/>
     </row>
-    <row r="962" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="962" ht="12.75" customHeight="true">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -35555,7 +36026,7 @@
       <c r="AG962" s="1"/>
       <c r="AH962" s="1"/>
     </row>
-    <row r="963" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="963" ht="12.75" customHeight="true">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -35591,7 +36062,7 @@
       <c r="AG963" s="1"/>
       <c r="AH963" s="1"/>
     </row>
-    <row r="964" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="964" ht="12.75" customHeight="true">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -35627,7 +36098,7 @@
       <c r="AG964" s="1"/>
       <c r="AH964" s="1"/>
     </row>
-    <row r="965" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="965" ht="12.75" customHeight="true">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -35663,7 +36134,7 @@
       <c r="AG965" s="1"/>
       <c r="AH965" s="1"/>
     </row>
-    <row r="966" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="966" ht="12.75" customHeight="true">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -35699,7 +36170,7 @@
       <c r="AG966" s="1"/>
       <c r="AH966" s="1"/>
     </row>
-    <row r="967" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="967" ht="12.75" customHeight="true">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -35735,7 +36206,7 @@
       <c r="AG967" s="1"/>
       <c r="AH967" s="1"/>
     </row>
-    <row r="968" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="968" ht="12.75" customHeight="true">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -35771,7 +36242,7 @@
       <c r="AG968" s="1"/>
       <c r="AH968" s="1"/>
     </row>
-    <row r="969" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="969" ht="12.75" customHeight="true">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -35807,7 +36278,7 @@
       <c r="AG969" s="1"/>
       <c r="AH969" s="1"/>
     </row>
-    <row r="970" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="970" ht="12.75" customHeight="true">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -35843,7 +36314,7 @@
       <c r="AG970" s="1"/>
       <c r="AH970" s="1"/>
     </row>
-    <row r="971" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="971" ht="12.75" customHeight="true">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -35879,7 +36350,7 @@
       <c r="AG971" s="1"/>
       <c r="AH971" s="1"/>
     </row>
-    <row r="972" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="972" ht="12.75" customHeight="true">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -35915,7 +36386,7 @@
       <c r="AG972" s="1"/>
       <c r="AH972" s="1"/>
     </row>
-    <row r="973" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="973" ht="12.75" customHeight="true">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -35951,7 +36422,7 @@
       <c r="AG973" s="1"/>
       <c r="AH973" s="1"/>
     </row>
-    <row r="974" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="974" ht="12.75" customHeight="true">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -35987,7 +36458,7 @@
       <c r="AG974" s="1"/>
       <c r="AH974" s="1"/>
     </row>
-    <row r="975" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="975" ht="12.75" customHeight="true">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -36023,7 +36494,7 @@
       <c r="AG975" s="1"/>
       <c r="AH975" s="1"/>
     </row>
-    <row r="976" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="976" ht="12.75" customHeight="true">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -36059,7 +36530,7 @@
       <c r="AG976" s="1"/>
       <c r="AH976" s="1"/>
     </row>
-    <row r="977" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="977" ht="12.75" customHeight="true">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -36095,7 +36566,7 @@
       <c r="AG977" s="1"/>
       <c r="AH977" s="1"/>
     </row>
-    <row r="978" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="978" ht="12.75" customHeight="true">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -36131,7 +36602,7 @@
       <c r="AG978" s="1"/>
       <c r="AH978" s="1"/>
     </row>
-    <row r="979" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="979" ht="12.75" customHeight="true">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -36167,7 +36638,7 @@
       <c r="AG979" s="1"/>
       <c r="AH979" s="1"/>
     </row>
-    <row r="980" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="980" ht="12.75" customHeight="true">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -36203,7 +36674,7 @@
       <c r="AG980" s="1"/>
       <c r="AH980" s="1"/>
     </row>
-    <row r="981" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="981" ht="12.75" customHeight="true">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -36239,7 +36710,7 @@
       <c r="AG981" s="1"/>
       <c r="AH981" s="1"/>
     </row>
-    <row r="982" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="982" ht="12.75" customHeight="true">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -36275,7 +36746,7 @@
       <c r="AG982" s="1"/>
       <c r="AH982" s="1"/>
     </row>
-    <row r="983" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="983" ht="12.75" customHeight="true">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -36311,7 +36782,7 @@
       <c r="AG983" s="1"/>
       <c r="AH983" s="1"/>
     </row>
-    <row r="984" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="984" ht="12.75" customHeight="true">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -36347,7 +36818,7 @@
       <c r="AG984" s="1"/>
       <c r="AH984" s="1"/>
     </row>
-    <row r="985" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="985" ht="12.75" customHeight="true">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -36383,7 +36854,7 @@
       <c r="AG985" s="1"/>
       <c r="AH985" s="1"/>
     </row>
-    <row r="986" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="986" ht="12.75" customHeight="true">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -36419,7 +36890,7 @@
       <c r="AG986" s="1"/>
       <c r="AH986" s="1"/>
     </row>
-    <row r="987" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="987" ht="12.75" customHeight="true">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -36455,7 +36926,7 @@
       <c r="AG987" s="1"/>
       <c r="AH987" s="1"/>
     </row>
-    <row r="988" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="988" ht="12.75" customHeight="true">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -36491,7 +36962,7 @@
       <c r="AG988" s="1"/>
       <c r="AH988" s="1"/>
     </row>
-    <row r="989" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="989" ht="12.75" customHeight="true">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -36527,7 +36998,7 @@
       <c r="AG989" s="1"/>
       <c r="AH989" s="1"/>
     </row>
-    <row r="990" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="990" ht="12.75" customHeight="true">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -36563,7 +37034,7 @@
       <c r="AG990" s="1"/>
       <c r="AH990" s="1"/>
     </row>
-    <row r="991" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="991" ht="12.75" customHeight="true">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -36599,7 +37070,7 @@
       <c r="AG991" s="1"/>
       <c r="AH991" s="1"/>
     </row>
-    <row r="992" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="992" ht="12.75" customHeight="true">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -36635,7 +37106,7 @@
       <c r="AG992" s="1"/>
       <c r="AH992" s="1"/>
     </row>
-    <row r="993" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="993" ht="12.75" customHeight="true">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -36671,7 +37142,7 @@
       <c r="AG993" s="1"/>
       <c r="AH993" s="1"/>
     </row>
-    <row r="994" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="994" ht="12.75" customHeight="true">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -36707,7 +37178,7 @@
       <c r="AG994" s="1"/>
       <c r="AH994" s="1"/>
     </row>
-    <row r="995" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="995" ht="12.75" customHeight="true">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -36743,7 +37214,7 @@
       <c r="AG995" s="1"/>
       <c r="AH995" s="1"/>
     </row>
-    <row r="996" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="996" ht="12.75" customHeight="true">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -36779,7 +37250,7 @@
       <c r="AG996" s="1"/>
       <c r="AH996" s="1"/>
     </row>
-    <row r="997" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="997" ht="12.75" customHeight="true">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -36815,7 +37286,7 @@
       <c r="AG997" s="1"/>
       <c r="AH997" s="1"/>
     </row>
-    <row r="998" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="998" ht="12.75" customHeight="true">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -36851,7 +37322,7 @@
       <c r="AG998" s="1"/>
       <c r="AH998" s="1"/>
     </row>
-    <row r="999" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="999" ht="12.75" customHeight="true">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -36887,7 +37358,7 @@
       <c r="AG999" s="1"/>
       <c r="AH999" s="1"/>
     </row>
-    <row r="1000" ht="12.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1000" ht="12.75" customHeight="true">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -36957,11 +37428,9 @@
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="C27:E27"/>
   </mergeCells>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;A</oddHeader>
-    <oddFooter>&amp;CPágina &amp;P</oddFooter>
-  </headerFooter>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <headerFooter alignWithMargins="1"/>
 </worksheet>
 </file>